--- a/AAAGameData/Languages/Hindi.xlsx
+++ b/AAAGameData/Languages/Hindi.xlsx
@@ -28,6 +28,17 @@
         </d:r>
       </text>
     </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <rPr>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t xml:space="preserve">多语言Key</t>
+        </d:r>
+      </text>
+    </comment>
     <comment ref="C1" authorId="0">
       <text>
         <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
@@ -39,23 +50,12 @@
         </d:r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0">
-      <text>
-        <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <rPr>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t xml:space="preserve">多语言Key</t>
-        </d:r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>ArrowMazeOverUIForm.GameOver</t>
   </si>
@@ -196,6 +196,9 @@
   </si>
   <si>
     <t>MakeupUIForm.title</t>
+  </si>
+  <si>
+    <t>MakeupUIForm.txtBalance</t>
   </si>
   <si>
     <t>PrelevelUIForm.txtLevel</t>
@@ -420,6 +423,10 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp49.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -443,6 +450,198 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -459,10 +658,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1025">
+            <xdr:cNvPr hidden="1" name="A1" id="1073">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1025"/>
+                  <a14:compatExt spid="_x0000_s1073"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -545,10 +744,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1026">
+            <xdr:cNvPr hidden="1" name="A2" id="1074">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1026"/>
+                  <a14:compatExt spid="_x0000_s1074"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -631,10 +830,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1027">
+            <xdr:cNvPr hidden="1" name="A3" id="1075">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1027"/>
+                  <a14:compatExt spid="_x0000_s1075"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -717,10 +916,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1028">
+            <xdr:cNvPr hidden="1" name="A4" id="1076">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1028"/>
+                  <a14:compatExt spid="_x0000_s1076"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -803,10 +1002,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1029">
+            <xdr:cNvPr hidden="1" name="A5" id="1077">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1029"/>
+                  <a14:compatExt spid="_x0000_s1077"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -889,10 +1088,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1030">
+            <xdr:cNvPr hidden="1" name="A6" id="1078">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1030"/>
+                  <a14:compatExt spid="_x0000_s1078"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -975,10 +1174,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1031">
+            <xdr:cNvPr hidden="1" name="A7" id="1079">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1031"/>
+                  <a14:compatExt spid="_x0000_s1079"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1061,10 +1260,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1032">
+            <xdr:cNvPr hidden="1" name="A8" id="1080">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1032"/>
+                  <a14:compatExt spid="_x0000_s1080"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1147,10 +1346,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1033">
+            <xdr:cNvPr hidden="1" name="A9" id="1081">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1033"/>
+                  <a14:compatExt spid="_x0000_s1081"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1233,10 +1432,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1034">
+            <xdr:cNvPr hidden="1" name="A10" id="1082">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1034"/>
+                  <a14:compatExt spid="_x0000_s1082"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1319,10 +1518,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1035">
+            <xdr:cNvPr hidden="1" name="A11" id="1083">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1035"/>
+                  <a14:compatExt spid="_x0000_s1083"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1405,10 +1604,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1036">
+            <xdr:cNvPr hidden="1" name="A12" id="1084">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1036"/>
+                  <a14:compatExt spid="_x0000_s1084"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1491,10 +1690,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1037">
+            <xdr:cNvPr hidden="1" name="A13" id="1085">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1037"/>
+                  <a14:compatExt spid="_x0000_s1085"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1577,10 +1776,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1038">
+            <xdr:cNvPr hidden="1" name="A14" id="1086">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1038"/>
+                  <a14:compatExt spid="_x0000_s1086"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1663,10 +1862,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1039">
+            <xdr:cNvPr hidden="1" name="A15" id="1087">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1039"/>
+                  <a14:compatExt spid="_x0000_s1087"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1749,10 +1948,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1040">
+            <xdr:cNvPr hidden="1" name="A16" id="1088">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1040"/>
+                  <a14:compatExt spid="_x0000_s1088"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1835,10 +2034,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1041">
+            <xdr:cNvPr hidden="1" name="A17" id="1089">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1041"/>
+                  <a14:compatExt spid="_x0000_s1089"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1921,10 +2120,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1042">
+            <xdr:cNvPr hidden="1" name="A18" id="1090">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1042"/>
+                  <a14:compatExt spid="_x0000_s1090"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2007,10 +2206,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1043">
+            <xdr:cNvPr hidden="1" name="A19" id="1091">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1043"/>
+                  <a14:compatExt spid="_x0000_s1091"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2093,10 +2292,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1044">
+            <xdr:cNvPr hidden="1" name="A20" id="1092">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1044"/>
+                  <a14:compatExt spid="_x0000_s1092"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2179,10 +2378,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1045">
+            <xdr:cNvPr hidden="1" name="A21" id="1093">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1045"/>
+                  <a14:compatExt spid="_x0000_s1093"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2265,10 +2464,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1046">
+            <xdr:cNvPr hidden="1" name="A22" id="1094">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1046"/>
+                  <a14:compatExt spid="_x0000_s1094"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2351,10 +2550,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1047">
+            <xdr:cNvPr hidden="1" name="A23" id="1095">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1047"/>
+                  <a14:compatExt spid="_x0000_s1095"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2437,10 +2636,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1048">
+            <xdr:cNvPr hidden="1" name="A24" id="1096">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1048"/>
+                  <a14:compatExt spid="_x0000_s1096"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2523,10 +2722,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1049">
+            <xdr:cNvPr hidden="1" name="A25" id="1097">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1049"/>
+                  <a14:compatExt spid="_x0000_s1097"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2609,10 +2808,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1050">
+            <xdr:cNvPr hidden="1" name="A26" id="1098">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1050"/>
+                  <a14:compatExt spid="_x0000_s1098"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2695,10 +2894,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1051">
+            <xdr:cNvPr hidden="1" name="A27" id="1099">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1051"/>
+                  <a14:compatExt spid="_x0000_s1099"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2781,10 +2980,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1052">
+            <xdr:cNvPr hidden="1" name="A28" id="1100">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1052"/>
+                  <a14:compatExt spid="_x0000_s1100"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2867,10 +3066,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1053">
+            <xdr:cNvPr hidden="1" name="A29" id="1101">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1053"/>
+                  <a14:compatExt spid="_x0000_s1101"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2953,10 +3152,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1054">
+            <xdr:cNvPr hidden="1" name="A30" id="1102">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1054"/>
+                  <a14:compatExt spid="_x0000_s1102"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3039,10 +3238,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1055">
+            <xdr:cNvPr hidden="1" name="A31" id="1103">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1055"/>
+                  <a14:compatExt spid="_x0000_s1103"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3125,10 +3324,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1056">
+            <xdr:cNvPr hidden="1" name="A32" id="1104">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1056"/>
+                  <a14:compatExt spid="_x0000_s1104"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3211,10 +3410,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1057">
+            <xdr:cNvPr hidden="1" name="A33" id="1105">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1057"/>
+                  <a14:compatExt spid="_x0000_s1105"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3297,10 +3496,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A34" id="1058">
+            <xdr:cNvPr hidden="1" name="A34" id="1106">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1058"/>
+                  <a14:compatExt spid="_x0000_s1106"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3383,10 +3582,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A35" id="1059">
+            <xdr:cNvPr hidden="1" name="A35" id="1107">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1059"/>
+                  <a14:compatExt spid="_x0000_s1107"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3469,10 +3668,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A36" id="1060">
+            <xdr:cNvPr hidden="1" name="A36" id="1108">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1060"/>
+                  <a14:compatExt spid="_x0000_s1108"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3555,10 +3754,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A37" id="1061">
+            <xdr:cNvPr hidden="1" name="A37" id="1109">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1061"/>
+                  <a14:compatExt spid="_x0000_s1109"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3641,10 +3840,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A38" id="1062">
+            <xdr:cNvPr hidden="1" name="A38" id="1110">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1062"/>
+                  <a14:compatExt spid="_x0000_s1110"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3727,10 +3926,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A39" id="1063">
+            <xdr:cNvPr hidden="1" name="A39" id="1111">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1063"/>
+                  <a14:compatExt spid="_x0000_s1111"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3813,10 +4012,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A40" id="1064">
+            <xdr:cNvPr hidden="1" name="A40" id="1112">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1064"/>
+                  <a14:compatExt spid="_x0000_s1112"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3899,10 +4098,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A41" id="1065">
+            <xdr:cNvPr hidden="1" name="A41" id="1113">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1065"/>
+                  <a14:compatExt spid="_x0000_s1113"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3985,10 +4184,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A42" id="1066">
+            <xdr:cNvPr hidden="1" name="A42" id="1114">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1066"/>
+                  <a14:compatExt spid="_x0000_s1114"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4071,10 +4270,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A43" id="1067">
+            <xdr:cNvPr hidden="1" name="A43" id="1115">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1067"/>
+                  <a14:compatExt spid="_x0000_s1115"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4157,10 +4356,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A44" id="1068">
+            <xdr:cNvPr hidden="1" name="A44" id="1116">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1068"/>
+                  <a14:compatExt spid="_x0000_s1116"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4243,10 +4442,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A45" id="1069">
+            <xdr:cNvPr hidden="1" name="A45" id="1117">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1069"/>
+                  <a14:compatExt spid="_x0000_s1117"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4329,10 +4528,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A46" id="1070">
+            <xdr:cNvPr hidden="1" name="A46" id="1118">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1070"/>
+                  <a14:compatExt spid="_x0000_s1118"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4415,10 +4614,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A47" id="1071">
+            <xdr:cNvPr hidden="1" name="A47" id="1119">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1071"/>
+                  <a14:compatExt spid="_x0000_s1119"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4501,10 +4700,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A48" id="1072">
+            <xdr:cNvPr hidden="1" name="A48" id="1120">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1072"/>
+                  <a14:compatExt spid="_x0000_s1120"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4570,12 +4769,98 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>48</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>49</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A49" id="1121">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1121"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -5015,6 +5300,15 @@
         <v>1</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="1"/>
+      <c r="B49" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="C49" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
   <drawing r:id="rId1"/>
@@ -5024,7 +5318,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1025" r:id="rId2" name="A1">
+            <control shapeId="1073" r:id="rId52" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5046,7 +5340,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1026" r:id="rId4" name="A2">
+            <control shapeId="1074" r:id="rId53" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5068,7 +5362,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1027" r:id="rId5" name="A3">
+            <control shapeId="1075" r:id="rId54" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5090,7 +5384,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1028" r:id="rId6" name="A4">
+            <control shapeId="1076" r:id="rId55" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5112,7 +5406,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1029" r:id="rId7" name="A5">
+            <control shapeId="1077" r:id="rId56" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5134,7 +5428,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1030" r:id="rId8" name="A6">
+            <control shapeId="1078" r:id="rId57" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5156,7 +5450,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1031" r:id="rId9" name="A7">
+            <control shapeId="1079" r:id="rId58" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5178,7 +5472,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1032" r:id="rId10" name="A8">
+            <control shapeId="1080" r:id="rId59" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5200,7 +5494,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1033" r:id="rId11" name="A9">
+            <control shapeId="1081" r:id="rId60" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5222,7 +5516,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1034" r:id="rId12" name="A10">
+            <control shapeId="1082" r:id="rId61" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5244,7 +5538,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1035" r:id="rId13" name="A11">
+            <control shapeId="1083" r:id="rId62" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5266,7 +5560,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1036" r:id="rId14" name="A12">
+            <control shapeId="1084" r:id="rId63" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5288,7 +5582,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1037" r:id="rId15" name="A13">
+            <control shapeId="1085" r:id="rId64" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5310,7 +5604,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1038" r:id="rId16" name="A14">
+            <control shapeId="1086" r:id="rId65" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5332,7 +5626,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1039" r:id="rId17" name="A15">
+            <control shapeId="1087" r:id="rId66" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5354,7 +5648,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1040" r:id="rId18" name="A16">
+            <control shapeId="1088" r:id="rId67" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5376,7 +5670,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1041" r:id="rId19" name="A17">
+            <control shapeId="1089" r:id="rId68" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5398,7 +5692,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1042" r:id="rId20" name="A18">
+            <control shapeId="1090" r:id="rId69" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5420,7 +5714,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1043" r:id="rId21" name="A19">
+            <control shapeId="1091" r:id="rId70" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5442,7 +5736,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1044" r:id="rId22" name="A20">
+            <control shapeId="1092" r:id="rId71" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5464,7 +5758,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1045" r:id="rId23" name="A21">
+            <control shapeId="1093" r:id="rId72" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5486,7 +5780,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1046" r:id="rId24" name="A22">
+            <control shapeId="1094" r:id="rId73" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5508,7 +5802,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1047" r:id="rId25" name="A23">
+            <control shapeId="1095" r:id="rId74" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5530,7 +5824,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1048" r:id="rId26" name="A24">
+            <control shapeId="1096" r:id="rId75" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5552,7 +5846,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1049" r:id="rId27" name="A25">
+            <control shapeId="1097" r:id="rId76" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5574,7 +5868,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1050" r:id="rId28" name="A26">
+            <control shapeId="1098" r:id="rId77" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5596,7 +5890,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1051" r:id="rId29" name="A27">
+            <control shapeId="1099" r:id="rId78" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5618,7 +5912,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1052" r:id="rId30" name="A28">
+            <control shapeId="1100" r:id="rId79" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5640,7 +5934,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1053" r:id="rId31" name="A29">
+            <control shapeId="1101" r:id="rId80" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5662,7 +5956,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1054" r:id="rId32" name="A30">
+            <control shapeId="1102" r:id="rId81" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5684,7 +5978,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1055" r:id="rId33" name="A31">
+            <control shapeId="1103" r:id="rId82" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5706,7 +6000,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1056" r:id="rId34" name="A32">
+            <control shapeId="1104" r:id="rId83" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5728,7 +6022,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1057" r:id="rId35" name="A33">
+            <control shapeId="1105" r:id="rId84" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5750,7 +6044,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId36" name="A34">
+            <control shapeId="1106" r:id="rId85" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5772,7 +6066,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId37" name="A35">
+            <control shapeId="1107" r:id="rId86" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5794,7 +6088,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId38" name="A36">
+            <control shapeId="1108" r:id="rId87" name="A36">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5816,7 +6110,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId39" name="A37">
+            <control shapeId="1109" r:id="rId88" name="A37">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5838,7 +6132,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId40" name="A38">
+            <control shapeId="1110" r:id="rId89" name="A38">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5860,7 +6154,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId41" name="A39">
+            <control shapeId="1111" r:id="rId90" name="A39">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5882,7 +6176,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId42" name="A40">
+            <control shapeId="1112" r:id="rId91" name="A40">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5904,7 +6198,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1065" r:id="rId43" name="A41">
+            <control shapeId="1113" r:id="rId92" name="A41">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5926,7 +6220,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1066" r:id="rId44" name="A42">
+            <control shapeId="1114" r:id="rId93" name="A42">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5948,7 +6242,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1067" r:id="rId45" name="A43">
+            <control shapeId="1115" r:id="rId94" name="A43">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5970,7 +6264,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1068" r:id="rId46" name="A44">
+            <control shapeId="1116" r:id="rId95" name="A44">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5992,7 +6286,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId47" name="A45">
+            <control shapeId="1117" r:id="rId96" name="A45">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6014,7 +6308,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" r:id="rId48" name="A46">
+            <control shapeId="1118" r:id="rId97" name="A46">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6036,7 +6330,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1071" r:id="rId49" name="A47">
+            <control shapeId="1119" r:id="rId98" name="A47">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6058,7 +6352,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId50" name="A48">
+            <control shapeId="1120" r:id="rId99" name="A48">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6071,6 +6365,28 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>285750</xdr:colOff>
                     <xdr:row>48</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1121" r:id="rId100" name="A49">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>48</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>49</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>

--- a/AAAGameData/Languages/Hindi.xlsx
+++ b/AAAGameData/Languages/Hindi.xlsx
@@ -55,24 +55,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
-    <t>ArrowMazeOverUIForm.GameOver</t>
+    <t>AddBallsUIForm.ballTxt</t>
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>AddBallsUIForm.continueTxt</t>
+  </si>
+  <si>
+    <t>ArrowMazeOverUIForm.GameOver</t>
   </si>
   <si>
     <t>ArrowMazeOverUIForm.restart</t>
   </si>
   <si>
     <t>ArrowMazeOverUIForm.Revive</t>
-  </si>
-  <si>
-    <t>ArrowMazeUIForm.elimanateHit</t>
-  </si>
-  <si>
-    <t>ArrowMazeUIForm.LevelTxt</t>
   </si>
   <si>
     <t>ArrowPrivacyPolicyUIForm.title</t>
@@ -129,6 +129,9 @@
     <t>ArrowWithdrawalInfoItem.infoTxt</t>
   </si>
   <si>
+    <t>CoinRewardUIForm.titletxt</t>
+  </si>
+  <si>
     <t>Enteraccountnumber</t>
   </si>
   <si>
@@ -159,6 +162,15 @@
     <t>GuidTxt6</t>
   </si>
   <si>
+    <t>HallTabUIForm.home</t>
+  </si>
+  <si>
+    <t>HallTabUIForm.setting</t>
+  </si>
+  <si>
+    <t>HallTabUIForm.task</t>
+  </si>
+  <si>
     <t>InfoErrTips1</t>
   </si>
   <si>
@@ -180,6 +192,12 @@
     <t>InfoErrTips7</t>
   </si>
   <si>
+    <t>LevelCompleteUIForm.complete</t>
+  </si>
+  <si>
+    <t>LevelCompleteUIForm.leveltxt</t>
+  </si>
+  <si>
     <t>MakeUpFail</t>
   </si>
   <si>
@@ -189,10 +207,22 @@
     <t>makeupInfoHint2</t>
   </si>
   <si>
+    <t>MakeupPaymentUIForm.desc</t>
+  </si>
+  <si>
+    <t>MakeupPaymentUIForm.titletxt</t>
+  </si>
+  <si>
     <t>MakeUpStep1</t>
   </si>
   <si>
     <t>MakeUpStep2</t>
+  </si>
+  <si>
+    <t>MakeupUIForm.input</t>
+  </si>
+  <si>
+    <t>MakeupUIForm.record</t>
   </si>
   <si>
     <t>MakeupUIForm.title</t>
@@ -201,7 +231,25 @@
     <t>MakeupUIForm.txtBalance</t>
   </si>
   <si>
+    <t>PcardGiftUIForm.desc</t>
+  </si>
+  <si>
     <t>PrelevelUIForm.txtLevel</t>
+  </si>
+  <si>
+    <t>QuitConfirmUIForm.desc</t>
+  </si>
+  <si>
+    <t>QuitConfirmUIForm.quitTxt</t>
+  </si>
+  <si>
+    <t>SettingPageUIForm.continue</t>
+  </si>
+  <si>
+    <t>SettingPageUIForm.privacy</t>
+  </si>
+  <si>
+    <t>SettingPageUIForm.quit</t>
   </si>
   <si>
     <t>TaskItem.infoTxt</t>
@@ -316,7 +364,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
@@ -364,15 +412,15 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp35.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp36.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp37.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp38.xml><?xml version="1.0" encoding="utf-8"?>
@@ -408,7 +456,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp45.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp46.xml><?xml version="1.0" encoding="utf-8"?>
@@ -416,22 +464,86 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp47.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp48.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp49.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp50.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp51.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp52.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp53.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp54.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp55.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp56.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp57.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp58.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp59.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp60.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp61.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp62.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp63.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp64.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp65.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -642,6 +754,1650 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -658,10 +2414,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1073">
+            <xdr:cNvPr hidden="1" name="A1" id="1090">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1073"/>
+                  <a14:compatExt spid="_x0000_s1090"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -744,10 +2500,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1074">
+            <xdr:cNvPr hidden="1" name="A2" id="1091">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1074"/>
+                  <a14:compatExt spid="_x0000_s1091"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -830,10 +2586,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1075">
+            <xdr:cNvPr hidden="1" name="A3" id="1092">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1075"/>
+                  <a14:compatExt spid="_x0000_s1092"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -916,10 +2672,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1076">
+            <xdr:cNvPr hidden="1" name="A4" id="1093">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1076"/>
+                  <a14:compatExt spid="_x0000_s1093"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1002,10 +2758,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1077">
+            <xdr:cNvPr hidden="1" name="A5" id="1094">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1077"/>
+                  <a14:compatExt spid="_x0000_s1094"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1088,10 +2844,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1078">
+            <xdr:cNvPr hidden="1" name="A6" id="1095">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1078"/>
+                  <a14:compatExt spid="_x0000_s1095"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1174,10 +2930,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1079">
+            <xdr:cNvPr hidden="1" name="A7" id="1096">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1079"/>
+                  <a14:compatExt spid="_x0000_s1096"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1260,10 +3016,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1080">
+            <xdr:cNvPr hidden="1" name="A8" id="1097">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1080"/>
+                  <a14:compatExt spid="_x0000_s1097"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1346,10 +3102,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1081">
+            <xdr:cNvPr hidden="1" name="A9" id="1098">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1081"/>
+                  <a14:compatExt spid="_x0000_s1098"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1432,10 +3188,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1082">
+            <xdr:cNvPr hidden="1" name="A10" id="1099">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1082"/>
+                  <a14:compatExt spid="_x0000_s1099"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1518,10 +3274,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1083">
+            <xdr:cNvPr hidden="1" name="A11" id="1100">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1083"/>
+                  <a14:compatExt spid="_x0000_s1100"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1604,10 +3360,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1084">
+            <xdr:cNvPr hidden="1" name="A12" id="1101">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1084"/>
+                  <a14:compatExt spid="_x0000_s1101"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1690,10 +3446,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1085">
+            <xdr:cNvPr hidden="1" name="A13" id="1102">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1085"/>
+                  <a14:compatExt spid="_x0000_s1102"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1776,10 +3532,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1086">
+            <xdr:cNvPr hidden="1" name="A14" id="1103">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1086"/>
+                  <a14:compatExt spid="_x0000_s1103"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1862,10 +3618,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1087">
+            <xdr:cNvPr hidden="1" name="A15" id="1104">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1087"/>
+                  <a14:compatExt spid="_x0000_s1104"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -1948,10 +3704,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1088">
+            <xdr:cNvPr hidden="1" name="A16" id="1105">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1088"/>
+                  <a14:compatExt spid="_x0000_s1105"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2034,10 +3790,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1089">
+            <xdr:cNvPr hidden="1" name="A17" id="1106">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1089"/>
+                  <a14:compatExt spid="_x0000_s1106"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2120,10 +3876,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1090">
+            <xdr:cNvPr hidden="1" name="A18" id="1107">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1090"/>
+                  <a14:compatExt spid="_x0000_s1107"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2206,10 +3962,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1091">
+            <xdr:cNvPr hidden="1" name="A19" id="1108">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1091"/>
+                  <a14:compatExt spid="_x0000_s1108"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2292,10 +4048,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1092">
+            <xdr:cNvPr hidden="1" name="A20" id="1109">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1092"/>
+                  <a14:compatExt spid="_x0000_s1109"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2378,10 +4134,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1093">
+            <xdr:cNvPr hidden="1" name="A21" id="1110">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1093"/>
+                  <a14:compatExt spid="_x0000_s1110"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2464,10 +4220,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1094">
+            <xdr:cNvPr hidden="1" name="A22" id="1111">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1094"/>
+                  <a14:compatExt spid="_x0000_s1111"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2550,10 +4306,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1095">
+            <xdr:cNvPr hidden="1" name="A23" id="1112">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1095"/>
+                  <a14:compatExt spid="_x0000_s1112"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2636,10 +4392,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1096">
+            <xdr:cNvPr hidden="1" name="A24" id="1113">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1096"/>
+                  <a14:compatExt spid="_x0000_s1113"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2722,10 +4478,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1097">
+            <xdr:cNvPr hidden="1" name="A25" id="1114">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1097"/>
+                  <a14:compatExt spid="_x0000_s1114"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2808,10 +4564,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1098">
+            <xdr:cNvPr hidden="1" name="A26" id="1115">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1098"/>
+                  <a14:compatExt spid="_x0000_s1115"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2894,10 +4650,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1099">
+            <xdr:cNvPr hidden="1" name="A27" id="1116">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1099"/>
+                  <a14:compatExt spid="_x0000_s1116"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2980,10 +4736,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1100">
+            <xdr:cNvPr hidden="1" name="A28" id="1117">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1100"/>
+                  <a14:compatExt spid="_x0000_s1117"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3066,10 +4822,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1101">
+            <xdr:cNvPr hidden="1" name="A29" id="1118">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1101"/>
+                  <a14:compatExt spid="_x0000_s1118"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3152,10 +4908,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1102">
+            <xdr:cNvPr hidden="1" name="A30" id="1119">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1102"/>
+                  <a14:compatExt spid="_x0000_s1119"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3238,10 +4994,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1103">
+            <xdr:cNvPr hidden="1" name="A31" id="1120">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1103"/>
+                  <a14:compatExt spid="_x0000_s1120"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3324,10 +5080,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1104">
+            <xdr:cNvPr hidden="1" name="A32" id="1121">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1104"/>
+                  <a14:compatExt spid="_x0000_s1121"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3410,10 +5166,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1105">
+            <xdr:cNvPr hidden="1" name="A33" id="1122">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1105"/>
+                  <a14:compatExt spid="_x0000_s1122"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3496,10 +5252,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A34" id="1106">
+            <xdr:cNvPr hidden="1" name="A34" id="1123">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1106"/>
+                  <a14:compatExt spid="_x0000_s1123"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3582,10 +5338,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A35" id="1107">
+            <xdr:cNvPr hidden="1" name="A35" id="1124">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1107"/>
+                  <a14:compatExt spid="_x0000_s1124"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3668,10 +5424,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A36" id="1108">
+            <xdr:cNvPr hidden="1" name="A36" id="1125">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1108"/>
+                  <a14:compatExt spid="_x0000_s1125"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3754,10 +5510,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A37" id="1109">
+            <xdr:cNvPr hidden="1" name="A37" id="1126">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1109"/>
+                  <a14:compatExt spid="_x0000_s1126"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3840,10 +5596,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A38" id="1110">
+            <xdr:cNvPr hidden="1" name="A38" id="1127">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1110"/>
+                  <a14:compatExt spid="_x0000_s1127"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3926,10 +5682,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A39" id="1111">
+            <xdr:cNvPr hidden="1" name="A39" id="1128">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1111"/>
+                  <a14:compatExt spid="_x0000_s1128"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4012,10 +5768,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A40" id="1112">
+            <xdr:cNvPr hidden="1" name="A40" id="1129">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1112"/>
+                  <a14:compatExt spid="_x0000_s1129"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4098,10 +5854,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A41" id="1113">
+            <xdr:cNvPr hidden="1" name="A41" id="1130">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1113"/>
+                  <a14:compatExt spid="_x0000_s1130"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4184,10 +5940,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A42" id="1114">
+            <xdr:cNvPr hidden="1" name="A42" id="1131">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1114"/>
+                  <a14:compatExt spid="_x0000_s1131"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4270,10 +6026,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A43" id="1115">
+            <xdr:cNvPr hidden="1" name="A43" id="1132">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1115"/>
+                  <a14:compatExt spid="_x0000_s1132"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4356,10 +6112,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A44" id="1116">
+            <xdr:cNvPr hidden="1" name="A44" id="1133">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1116"/>
+                  <a14:compatExt spid="_x0000_s1133"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4442,10 +6198,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A45" id="1117">
+            <xdr:cNvPr hidden="1" name="A45" id="1134">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1117"/>
+                  <a14:compatExt spid="_x0000_s1134"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4528,10 +6284,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A46" id="1118">
+            <xdr:cNvPr hidden="1" name="A46" id="1135">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1118"/>
+                  <a14:compatExt spid="_x0000_s1135"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4614,10 +6370,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A47" id="1119">
+            <xdr:cNvPr hidden="1" name="A47" id="1136">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1119"/>
+                  <a14:compatExt spid="_x0000_s1136"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4700,10 +6456,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A48" id="1120">
+            <xdr:cNvPr hidden="1" name="A48" id="1137">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1120"/>
+                  <a14:compatExt spid="_x0000_s1137"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4786,10 +6542,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A49" id="1121">
+            <xdr:cNvPr hidden="1" name="A49" id="1138">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1121"/>
+                  <a14:compatExt spid="_x0000_s1138"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4855,12 +6611,1388 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>49</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>50</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A50" id="1139">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1139"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>50</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>51</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A51" id="1140">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1140"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>51</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>52</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A52" id="1141">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1141"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>52</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>53</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A53" id="1142">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1142"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>53</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>54</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A54" id="1143">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1143"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>54</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>55</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A55" id="1144">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1144"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>55</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>56</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A56" id="1145">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1145"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>56</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>57</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A57" id="1146">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1146"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>57</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>58</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A58" id="1147">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1147"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>58</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>59</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A59" id="1148">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1148"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>59</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>60</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A60" id="1149">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1149"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>60</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>61</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A61" id="1150">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1150"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>61</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>62</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A62" id="1151">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1151"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>62</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>63</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A63" id="1152">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1152"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>63</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>64</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A64" id="1153">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1153"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>64</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>65</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A65" id="1154">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1154"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -5309,6 +8441,150 @@
         <v>1</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="1"/>
+      <c r="B50" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="C50" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1"/>
+      <c r="B51" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="C51" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1"/>
+      <c r="B52" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="C52" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1"/>
+      <c r="B53" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C53" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1"/>
+      <c r="B54" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C54" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1"/>
+      <c r="B55" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="C55" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1"/>
+      <c r="B56" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C56" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1"/>
+      <c r="B57" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="C57" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1"/>
+      <c r="B58" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="C58" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1"/>
+      <c r="B59" s="0" t="s">
+        <v>59</v>
+      </c>
+      <c r="C59" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1"/>
+      <c r="B60" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="C60" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1"/>
+      <c r="B61" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="C61" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1"/>
+      <c r="B62" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="C62" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1"/>
+      <c r="B63" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="C63" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1"/>
+      <c r="B64" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="C64" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1"/>
+      <c r="B65" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="C65" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
   <drawing r:id="rId1"/>
@@ -5318,7 +8594,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId52" name="A1">
+            <control shapeId="1090" r:id="rId456" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5340,7 +8616,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId53" name="A2">
+            <control shapeId="1091" r:id="rId457" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5362,7 +8638,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId54" name="A3">
+            <control shapeId="1092" r:id="rId458" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5384,7 +8660,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId55" name="A4">
+            <control shapeId="1093" r:id="rId459" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5406,7 +8682,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId56" name="A5">
+            <control shapeId="1094" r:id="rId460" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5428,7 +8704,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId57" name="A6">
+            <control shapeId="1095" r:id="rId461" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5450,7 +8726,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId58" name="A7">
+            <control shapeId="1096" r:id="rId462" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5472,7 +8748,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId59" name="A8">
+            <control shapeId="1097" r:id="rId463" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5494,7 +8770,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId60" name="A9">
+            <control shapeId="1098" r:id="rId464" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5516,7 +8792,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId61" name="A10">
+            <control shapeId="1099" r:id="rId465" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5538,7 +8814,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId62" name="A11">
+            <control shapeId="1100" r:id="rId466" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5560,7 +8836,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId63" name="A12">
+            <control shapeId="1101" r:id="rId467" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5582,7 +8858,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId64" name="A13">
+            <control shapeId="1102" r:id="rId468" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5604,7 +8880,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId65" name="A14">
+            <control shapeId="1103" r:id="rId469" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5626,7 +8902,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1087" r:id="rId66" name="A15">
+            <control shapeId="1104" r:id="rId470" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5648,7 +8924,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1088" r:id="rId67" name="A16">
+            <control shapeId="1105" r:id="rId471" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5670,7 +8946,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1089" r:id="rId68" name="A17">
+            <control shapeId="1106" r:id="rId472" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5692,7 +8968,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1090" r:id="rId69" name="A18">
+            <control shapeId="1107" r:id="rId473" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5714,7 +8990,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1091" r:id="rId70" name="A19">
+            <control shapeId="1108" r:id="rId474" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5736,7 +9012,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1092" r:id="rId71" name="A20">
+            <control shapeId="1109" r:id="rId475" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5758,7 +9034,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId72" name="A21">
+            <control shapeId="1110" r:id="rId476" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5780,7 +9056,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId73" name="A22">
+            <control shapeId="1111" r:id="rId477" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5802,7 +9078,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId74" name="A23">
+            <control shapeId="1112" r:id="rId478" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5824,7 +9100,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId75" name="A24">
+            <control shapeId="1113" r:id="rId479" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5846,7 +9122,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId76" name="A25">
+            <control shapeId="1114" r:id="rId480" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5868,7 +9144,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId77" name="A26">
+            <control shapeId="1115" r:id="rId481" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5890,7 +9166,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId78" name="A27">
+            <control shapeId="1116" r:id="rId482" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5912,7 +9188,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId79" name="A28">
+            <control shapeId="1117" r:id="rId483" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5934,7 +9210,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId80" name="A29">
+            <control shapeId="1118" r:id="rId484" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5956,7 +9232,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId81" name="A30">
+            <control shapeId="1119" r:id="rId485" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5978,7 +9254,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId82" name="A31">
+            <control shapeId="1120" r:id="rId486" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6000,7 +9276,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId83" name="A32">
+            <control shapeId="1121" r:id="rId487" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6022,7 +9298,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId84" name="A33">
+            <control shapeId="1122" r:id="rId488" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6044,7 +9320,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId85" name="A34">
+            <control shapeId="1123" r:id="rId489" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6066,7 +9342,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId86" name="A35">
+            <control shapeId="1124" r:id="rId490" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6088,7 +9364,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId87" name="A36">
+            <control shapeId="1125" r:id="rId491" name="A36">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6110,7 +9386,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId88" name="A37">
+            <control shapeId="1126" r:id="rId492" name="A37">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6132,7 +9408,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId89" name="A38">
+            <control shapeId="1127" r:id="rId493" name="A38">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6154,7 +9430,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1111" r:id="rId90" name="A39">
+            <control shapeId="1128" r:id="rId494" name="A39">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6176,7 +9452,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1112" r:id="rId91" name="A40">
+            <control shapeId="1129" r:id="rId495" name="A40">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6198,7 +9474,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1113" r:id="rId92" name="A41">
+            <control shapeId="1130" r:id="rId496" name="A41">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6220,7 +9496,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1114" r:id="rId93" name="A42">
+            <control shapeId="1131" r:id="rId497" name="A42">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6242,7 +9518,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1115" r:id="rId94" name="A43">
+            <control shapeId="1132" r:id="rId498" name="A43">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6264,7 +9540,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1116" r:id="rId95" name="A44">
+            <control shapeId="1133" r:id="rId499" name="A44">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6286,7 +9562,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1117" r:id="rId96" name="A45">
+            <control shapeId="1134" r:id="rId500" name="A45">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6308,7 +9584,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1118" r:id="rId97" name="A46">
+            <control shapeId="1135" r:id="rId501" name="A46">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6330,7 +9606,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1119" r:id="rId98" name="A47">
+            <control shapeId="1136" r:id="rId502" name="A47">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6352,7 +9628,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1120" r:id="rId99" name="A48">
+            <control shapeId="1137" r:id="rId503" name="A48">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6374,7 +9650,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1121" r:id="rId100" name="A49">
+            <control shapeId="1138" r:id="rId504" name="A49">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -6387,6 +9663,358 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>285750</xdr:colOff>
                     <xdr:row>49</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1139" r:id="rId505" name="A50">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>49</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>50</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1140" r:id="rId506" name="A51">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>50</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>51</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1141" r:id="rId507" name="A52">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>51</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>52</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1142" r:id="rId508" name="A53">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>52</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>53</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1143" r:id="rId509" name="A54">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>53</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>54</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1144" r:id="rId510" name="A55">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>54</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>55</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1145" r:id="rId511" name="A56">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>55</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>56</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1146" r:id="rId512" name="A57">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>56</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>57</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1147" r:id="rId513" name="A58">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>57</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>58</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1148" r:id="rId514" name="A59">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>58</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>59</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1149" r:id="rId515" name="A60">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>59</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>60</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1150" r:id="rId516" name="A61">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>60</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>61</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1151" r:id="rId517" name="A62">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>61</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>62</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1152" r:id="rId518" name="A63">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>62</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>63</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1153" r:id="rId519" name="A64">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>63</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>64</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1154" r:id="rId520" name="A65">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>64</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>65</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>

--- a/AAAGameData/Languages/Hindi.xlsx
+++ b/AAAGameData/Languages/Hindi.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
   <si>
     <t>AddBallsUIForm.ballTxt</t>
   </si>
@@ -129,6 +129,9 @@
     <t>ArrowWithdrawalInfoItem.infoTxt</t>
   </si>
   <si>
+    <t>claim</t>
+  </si>
+  <si>
     <t>CoinRewardUIForm.titletxt</t>
   </si>
   <si>
@@ -192,10 +195,13 @@
     <t>InfoErrTips7</t>
   </si>
   <si>
+    <t>level</t>
+  </si>
+  <si>
     <t>LevelCompleteUIForm.complete</t>
   </si>
   <si>
-    <t>LevelCompleteUIForm.leveltxt</t>
+    <t>LevelCompleteUIForm.next</t>
   </si>
   <si>
     <t>MakeUpFail</t>
@@ -232,9 +238,6 @@
   </si>
   <si>
     <t>PcardGiftUIForm.desc</t>
-  </si>
-  <si>
-    <t>PrelevelUIForm.txtLevel</t>
   </si>
   <si>
     <t>QuitConfirmUIForm.desc</t>
@@ -368,7 +371,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp26.xml><?xml version="1.0" encoding="utf-8"?>
@@ -412,7 +415,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp35.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp36.xml><?xml version="1.0" encoding="utf-8"?>
@@ -424,7 +427,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp38.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp39.xml><?xml version="1.0" encoding="utf-8"?>
@@ -456,7 +459,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp45.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp46.xml><?xml version="1.0" encoding="utf-8"?>
@@ -464,11 +467,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp47.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp48.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp49.xml><?xml version="1.0" encoding="utf-8"?>
@@ -480,27 +483,27 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp50.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp51.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp52.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp53.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp54.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ctrlProps/ctrlProp55.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp54.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp55.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp56.xml><?xml version="1.0" encoding="utf-8"?>
@@ -547,6 +550,10 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp66.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -2398,6 +2405,1066 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -2414,10 +3481,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1090">
+            <xdr:cNvPr hidden="1" name="A1" id="1092">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1090"/>
+                  <a14:compatExt spid="_x0000_s1092"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2500,10 +3567,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1091">
+            <xdr:cNvPr hidden="1" name="A2" id="1093">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1091"/>
+                  <a14:compatExt spid="_x0000_s1093"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2586,10 +3653,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1092">
+            <xdr:cNvPr hidden="1" name="A3" id="1094">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1092"/>
+                  <a14:compatExt spid="_x0000_s1094"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2672,10 +3739,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1093">
+            <xdr:cNvPr hidden="1" name="A4" id="1095">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1093"/>
+                  <a14:compatExt spid="_x0000_s1095"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2758,10 +3825,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1094">
+            <xdr:cNvPr hidden="1" name="A5" id="1096">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1094"/>
+                  <a14:compatExt spid="_x0000_s1096"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2844,10 +3911,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1095">
+            <xdr:cNvPr hidden="1" name="A6" id="1097">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1095"/>
+                  <a14:compatExt spid="_x0000_s1097"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -2930,10 +3997,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1096">
+            <xdr:cNvPr hidden="1" name="A7" id="1098">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1096"/>
+                  <a14:compatExt spid="_x0000_s1098"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3016,10 +4083,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1097">
+            <xdr:cNvPr hidden="1" name="A8" id="1099">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1097"/>
+                  <a14:compatExt spid="_x0000_s1099"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3102,10 +4169,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1098">
+            <xdr:cNvPr hidden="1" name="A9" id="1100">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1098"/>
+                  <a14:compatExt spid="_x0000_s1100"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3188,10 +4255,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1099">
+            <xdr:cNvPr hidden="1" name="A10" id="1101">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1099"/>
+                  <a14:compatExt spid="_x0000_s1101"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3274,10 +4341,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1100">
+            <xdr:cNvPr hidden="1" name="A11" id="1102">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1100"/>
+                  <a14:compatExt spid="_x0000_s1102"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3360,10 +4427,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1101">
+            <xdr:cNvPr hidden="1" name="A12" id="1103">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1101"/>
+                  <a14:compatExt spid="_x0000_s1103"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3446,10 +4513,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1102">
+            <xdr:cNvPr hidden="1" name="A13" id="1104">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1102"/>
+                  <a14:compatExt spid="_x0000_s1104"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3532,10 +4599,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1103">
+            <xdr:cNvPr hidden="1" name="A14" id="1105">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1103"/>
+                  <a14:compatExt spid="_x0000_s1105"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3618,10 +4685,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1104">
+            <xdr:cNvPr hidden="1" name="A15" id="1106">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1104"/>
+                  <a14:compatExt spid="_x0000_s1106"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3704,10 +4771,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1105">
+            <xdr:cNvPr hidden="1" name="A16" id="1107">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1105"/>
+                  <a14:compatExt spid="_x0000_s1107"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3790,10 +4857,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1106">
+            <xdr:cNvPr hidden="1" name="A17" id="1108">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1106"/>
+                  <a14:compatExt spid="_x0000_s1108"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3876,10 +4943,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1107">
+            <xdr:cNvPr hidden="1" name="A18" id="1109">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1107"/>
+                  <a14:compatExt spid="_x0000_s1109"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3962,10 +5029,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1108">
+            <xdr:cNvPr hidden="1" name="A19" id="1110">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1108"/>
+                  <a14:compatExt spid="_x0000_s1110"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4048,10 +5115,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1109">
+            <xdr:cNvPr hidden="1" name="A20" id="1111">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1109"/>
+                  <a14:compatExt spid="_x0000_s1111"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4134,10 +5201,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1110">
+            <xdr:cNvPr hidden="1" name="A21" id="1112">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1110"/>
+                  <a14:compatExt spid="_x0000_s1112"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4220,10 +5287,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1111">
+            <xdr:cNvPr hidden="1" name="A22" id="1113">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1111"/>
+                  <a14:compatExt spid="_x0000_s1113"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4306,10 +5373,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1112">
+            <xdr:cNvPr hidden="1" name="A23" id="1114">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1112"/>
+                  <a14:compatExt spid="_x0000_s1114"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4392,10 +5459,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1113">
+            <xdr:cNvPr hidden="1" name="A24" id="1115">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1113"/>
+                  <a14:compatExt spid="_x0000_s1115"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4478,10 +5545,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1114">
+            <xdr:cNvPr hidden="1" name="A25" id="1116">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1114"/>
+                  <a14:compatExt spid="_x0000_s1116"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4564,10 +5631,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1115">
+            <xdr:cNvPr hidden="1" name="A26" id="1117">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1115"/>
+                  <a14:compatExt spid="_x0000_s1117"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4650,10 +5717,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1116">
+            <xdr:cNvPr hidden="1" name="A27" id="1118">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1116"/>
+                  <a14:compatExt spid="_x0000_s1118"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4736,10 +5803,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1117">
+            <xdr:cNvPr hidden="1" name="A28" id="1119">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1117"/>
+                  <a14:compatExt spid="_x0000_s1119"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4822,10 +5889,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1118">
+            <xdr:cNvPr hidden="1" name="A29" id="1120">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1118"/>
+                  <a14:compatExt spid="_x0000_s1120"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4908,10 +5975,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1119">
+            <xdr:cNvPr hidden="1" name="A30" id="1121">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1119"/>
+                  <a14:compatExt spid="_x0000_s1121"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4994,10 +6061,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1120">
+            <xdr:cNvPr hidden="1" name="A31" id="1122">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1120"/>
+                  <a14:compatExt spid="_x0000_s1122"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5080,10 +6147,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1121">
+            <xdr:cNvPr hidden="1" name="A32" id="1123">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1121"/>
+                  <a14:compatExt spid="_x0000_s1123"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5166,10 +6233,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1122">
+            <xdr:cNvPr hidden="1" name="A33" id="1124">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1122"/>
+                  <a14:compatExt spid="_x0000_s1124"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5252,10 +6319,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A34" id="1123">
+            <xdr:cNvPr hidden="1" name="A34" id="1125">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1123"/>
+                  <a14:compatExt spid="_x0000_s1125"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5338,10 +6405,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A35" id="1124">
+            <xdr:cNvPr hidden="1" name="A35" id="1126">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1124"/>
+                  <a14:compatExt spid="_x0000_s1126"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5424,10 +6491,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A36" id="1125">
+            <xdr:cNvPr hidden="1" name="A36" id="1127">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1125"/>
+                  <a14:compatExt spid="_x0000_s1127"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5510,10 +6577,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A37" id="1126">
+            <xdr:cNvPr hidden="1" name="A37" id="1128">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1126"/>
+                  <a14:compatExt spid="_x0000_s1128"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5596,10 +6663,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A38" id="1127">
+            <xdr:cNvPr hidden="1" name="A38" id="1129">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1127"/>
+                  <a14:compatExt spid="_x0000_s1129"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5682,10 +6749,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A39" id="1128">
+            <xdr:cNvPr hidden="1" name="A39" id="1130">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1128"/>
+                  <a14:compatExt spid="_x0000_s1130"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5768,10 +6835,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A40" id="1129">
+            <xdr:cNvPr hidden="1" name="A40" id="1131">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1129"/>
+                  <a14:compatExt spid="_x0000_s1131"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5854,10 +6921,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A41" id="1130">
+            <xdr:cNvPr hidden="1" name="A41" id="1132">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1130"/>
+                  <a14:compatExt spid="_x0000_s1132"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5940,10 +7007,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A42" id="1131">
+            <xdr:cNvPr hidden="1" name="A42" id="1133">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1131"/>
+                  <a14:compatExt spid="_x0000_s1133"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6026,10 +7093,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A43" id="1132">
+            <xdr:cNvPr hidden="1" name="A43" id="1134">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1132"/>
+                  <a14:compatExt spid="_x0000_s1134"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6112,10 +7179,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A44" id="1133">
+            <xdr:cNvPr hidden="1" name="A44" id="1135">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1133"/>
+                  <a14:compatExt spid="_x0000_s1135"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6198,10 +7265,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A45" id="1134">
+            <xdr:cNvPr hidden="1" name="A45" id="1136">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1134"/>
+                  <a14:compatExt spid="_x0000_s1136"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6284,10 +7351,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A46" id="1135">
+            <xdr:cNvPr hidden="1" name="A46" id="1137">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1135"/>
+                  <a14:compatExt spid="_x0000_s1137"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6370,10 +7437,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A47" id="1136">
+            <xdr:cNvPr hidden="1" name="A47" id="1138">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1136"/>
+                  <a14:compatExt spid="_x0000_s1138"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6456,10 +7523,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A48" id="1137">
+            <xdr:cNvPr hidden="1" name="A48" id="1139">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1137"/>
+                  <a14:compatExt spid="_x0000_s1139"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6542,10 +7609,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A49" id="1138">
+            <xdr:cNvPr hidden="1" name="A49" id="1140">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1138"/>
+                  <a14:compatExt spid="_x0000_s1140"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6628,10 +7695,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A50" id="1139">
+            <xdr:cNvPr hidden="1" name="A50" id="1141">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1139"/>
+                  <a14:compatExt spid="_x0000_s1141"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6714,10 +7781,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A51" id="1140">
+            <xdr:cNvPr hidden="1" name="A51" id="1142">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1140"/>
+                  <a14:compatExt spid="_x0000_s1142"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6800,10 +7867,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A52" id="1141">
+            <xdr:cNvPr hidden="1" name="A52" id="1143">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1141"/>
+                  <a14:compatExt spid="_x0000_s1143"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6886,10 +7953,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A53" id="1142">
+            <xdr:cNvPr hidden="1" name="A53" id="1144">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1142"/>
+                  <a14:compatExt spid="_x0000_s1144"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6972,10 +8039,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A54" id="1143">
+            <xdr:cNvPr hidden="1" name="A54" id="1145">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1143"/>
+                  <a14:compatExt spid="_x0000_s1145"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7058,10 +8125,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A55" id="1144">
+            <xdr:cNvPr hidden="1" name="A55" id="1146">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1144"/>
+                  <a14:compatExt spid="_x0000_s1146"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7144,10 +8211,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A56" id="1145">
+            <xdr:cNvPr hidden="1" name="A56" id="1147">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1145"/>
+                  <a14:compatExt spid="_x0000_s1147"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7230,10 +8297,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A57" id="1146">
+            <xdr:cNvPr hidden="1" name="A57" id="1148">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1146"/>
+                  <a14:compatExt spid="_x0000_s1148"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7316,10 +8383,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A58" id="1147">
+            <xdr:cNvPr hidden="1" name="A58" id="1149">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1147"/>
+                  <a14:compatExt spid="_x0000_s1149"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7402,10 +8469,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A59" id="1148">
+            <xdr:cNvPr hidden="1" name="A59" id="1150">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1148"/>
+                  <a14:compatExt spid="_x0000_s1150"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7488,10 +8555,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A60" id="1149">
+            <xdr:cNvPr hidden="1" name="A60" id="1151">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1149"/>
+                  <a14:compatExt spid="_x0000_s1151"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7574,10 +8641,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A61" id="1150">
+            <xdr:cNvPr hidden="1" name="A61" id="1152">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1150"/>
+                  <a14:compatExt spid="_x0000_s1152"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7660,10 +8727,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A62" id="1151">
+            <xdr:cNvPr hidden="1" name="A62" id="1153">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1151"/>
+                  <a14:compatExt spid="_x0000_s1153"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7746,10 +8813,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A63" id="1152">
+            <xdr:cNvPr hidden="1" name="A63" id="1154">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1152"/>
+                  <a14:compatExt spid="_x0000_s1154"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7832,10 +8899,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A64" id="1153">
+            <xdr:cNvPr hidden="1" name="A64" id="1155">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1153"/>
+                  <a14:compatExt spid="_x0000_s1155"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7918,10 +8985,10 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A65" id="1154">
+            <xdr:cNvPr hidden="1" name="A65" id="1156">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1154"/>
+                  <a14:compatExt spid="_x0000_s1156"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7987,12 +9054,98 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>65</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>66</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A66" id="1157">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1157"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -8585,6 +9738,15 @@
         <v>1</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="1"/>
+      <c r="B66" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="C66" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <headerFooter/>
   <drawing r:id="rId1"/>
@@ -8594,7 +9756,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1090" r:id="rId456" name="A1">
+            <control shapeId="1092" r:id="rId717" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8616,7 +9778,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1091" r:id="rId457" name="A2">
+            <control shapeId="1093" r:id="rId718" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8638,7 +9800,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1092" r:id="rId458" name="A3">
+            <control shapeId="1094" r:id="rId719" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8660,7 +9822,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId459" name="A4">
+            <control shapeId="1095" r:id="rId720" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8682,7 +9844,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId460" name="A5">
+            <control shapeId="1096" r:id="rId721" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8704,7 +9866,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId461" name="A6">
+            <control shapeId="1097" r:id="rId722" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8726,7 +9888,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId462" name="A7">
+            <control shapeId="1098" r:id="rId723" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8748,7 +9910,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId463" name="A8">
+            <control shapeId="1099" r:id="rId724" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8770,7 +9932,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId464" name="A9">
+            <control shapeId="1100" r:id="rId725" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8792,7 +9954,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId465" name="A10">
+            <control shapeId="1101" r:id="rId726" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8814,7 +9976,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId466" name="A11">
+            <control shapeId="1102" r:id="rId727" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8836,7 +9998,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId467" name="A12">
+            <control shapeId="1103" r:id="rId728" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8858,7 +10020,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId468" name="A13">
+            <control shapeId="1104" r:id="rId729" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8880,7 +10042,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId469" name="A14">
+            <control shapeId="1105" r:id="rId730" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8902,7 +10064,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId470" name="A15">
+            <control shapeId="1106" r:id="rId731" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8924,7 +10086,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId471" name="A16">
+            <control shapeId="1107" r:id="rId732" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8946,7 +10108,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId472" name="A17">
+            <control shapeId="1108" r:id="rId733" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8968,7 +10130,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId473" name="A18">
+            <control shapeId="1109" r:id="rId734" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -8990,7 +10152,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId474" name="A19">
+            <control shapeId="1110" r:id="rId735" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9012,7 +10174,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId475" name="A20">
+            <control shapeId="1111" r:id="rId736" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9034,7 +10196,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId476" name="A21">
+            <control shapeId="1112" r:id="rId737" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9056,7 +10218,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1111" r:id="rId477" name="A22">
+            <control shapeId="1113" r:id="rId738" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9078,7 +10240,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1112" r:id="rId478" name="A23">
+            <control shapeId="1114" r:id="rId739" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9100,7 +10262,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1113" r:id="rId479" name="A24">
+            <control shapeId="1115" r:id="rId740" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9122,7 +10284,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1114" r:id="rId480" name="A25">
+            <control shapeId="1116" r:id="rId741" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9144,7 +10306,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1115" r:id="rId481" name="A26">
+            <control shapeId="1117" r:id="rId742" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9166,7 +10328,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1116" r:id="rId482" name="A27">
+            <control shapeId="1118" r:id="rId743" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9188,7 +10350,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1117" r:id="rId483" name="A28">
+            <control shapeId="1119" r:id="rId744" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9210,7 +10372,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1118" r:id="rId484" name="A29">
+            <control shapeId="1120" r:id="rId745" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9232,7 +10394,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1119" r:id="rId485" name="A30">
+            <control shapeId="1121" r:id="rId746" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9254,7 +10416,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1120" r:id="rId486" name="A31">
+            <control shapeId="1122" r:id="rId747" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9276,7 +10438,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1121" r:id="rId487" name="A32">
+            <control shapeId="1123" r:id="rId748" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9298,7 +10460,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1122" r:id="rId488" name="A33">
+            <control shapeId="1124" r:id="rId749" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9320,7 +10482,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1123" r:id="rId489" name="A34">
+            <control shapeId="1125" r:id="rId750" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9342,7 +10504,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1124" r:id="rId490" name="A35">
+            <control shapeId="1126" r:id="rId751" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9364,7 +10526,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1125" r:id="rId491" name="A36">
+            <control shapeId="1127" r:id="rId752" name="A36">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9386,7 +10548,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1126" r:id="rId492" name="A37">
+            <control shapeId="1128" r:id="rId753" name="A37">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9408,7 +10570,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1127" r:id="rId493" name="A38">
+            <control shapeId="1129" r:id="rId754" name="A38">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9430,7 +10592,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1128" r:id="rId494" name="A39">
+            <control shapeId="1130" r:id="rId755" name="A39">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9452,7 +10614,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1129" r:id="rId495" name="A40">
+            <control shapeId="1131" r:id="rId756" name="A40">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9474,7 +10636,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1130" r:id="rId496" name="A41">
+            <control shapeId="1132" r:id="rId757" name="A41">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9496,7 +10658,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1131" r:id="rId497" name="A42">
+            <control shapeId="1133" r:id="rId758" name="A42">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9518,7 +10680,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1132" r:id="rId498" name="A43">
+            <control shapeId="1134" r:id="rId759" name="A43">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9540,7 +10702,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1133" r:id="rId499" name="A44">
+            <control shapeId="1135" r:id="rId760" name="A44">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9562,7 +10724,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1134" r:id="rId500" name="A45">
+            <control shapeId="1136" r:id="rId761" name="A45">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9584,7 +10746,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1135" r:id="rId501" name="A46">
+            <control shapeId="1137" r:id="rId762" name="A46">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9606,7 +10768,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1136" r:id="rId502" name="A47">
+            <control shapeId="1138" r:id="rId763" name="A47">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9628,7 +10790,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1137" r:id="rId503" name="A48">
+            <control shapeId="1139" r:id="rId764" name="A48">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9650,7 +10812,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1138" r:id="rId504" name="A49">
+            <control shapeId="1140" r:id="rId765" name="A49">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9672,7 +10834,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1139" r:id="rId505" name="A50">
+            <control shapeId="1141" r:id="rId766" name="A50">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9694,7 +10856,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1140" r:id="rId506" name="A51">
+            <control shapeId="1142" r:id="rId767" name="A51">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9716,7 +10878,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1141" r:id="rId507" name="A52">
+            <control shapeId="1143" r:id="rId768" name="A52">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9738,7 +10900,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1142" r:id="rId508" name="A53">
+            <control shapeId="1144" r:id="rId769" name="A53">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9760,7 +10922,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1143" r:id="rId509" name="A54">
+            <control shapeId="1145" r:id="rId770" name="A54">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9782,7 +10944,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1144" r:id="rId510" name="A55">
+            <control shapeId="1146" r:id="rId771" name="A55">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9804,7 +10966,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1145" r:id="rId511" name="A56">
+            <control shapeId="1147" r:id="rId772" name="A56">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9826,7 +10988,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1146" r:id="rId512" name="A57">
+            <control shapeId="1148" r:id="rId773" name="A57">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9848,7 +11010,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1147" r:id="rId513" name="A58">
+            <control shapeId="1149" r:id="rId774" name="A58">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9870,7 +11032,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1148" r:id="rId514" name="A59">
+            <control shapeId="1150" r:id="rId775" name="A59">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9892,7 +11054,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1149" r:id="rId515" name="A60">
+            <control shapeId="1151" r:id="rId776" name="A60">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9914,7 +11076,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1150" r:id="rId516" name="A61">
+            <control shapeId="1152" r:id="rId777" name="A61">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9936,7 +11098,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1151" r:id="rId517" name="A62">
+            <control shapeId="1153" r:id="rId778" name="A62">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9958,7 +11120,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1152" r:id="rId518" name="A63">
+            <control shapeId="1154" r:id="rId779" name="A63">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9980,7 +11142,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1153" r:id="rId519" name="A64">
+            <control shapeId="1155" r:id="rId780" name="A64">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10002,7 +11164,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1154" r:id="rId520" name="A65">
+            <control shapeId="1156" r:id="rId781" name="A65">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10015,6 +11177,28 @@
                     <xdr:col>0</xdr:col>
                     <xdr:colOff>285750</xdr:colOff>
                     <xdr:row>65</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1157" r:id="rId782" name="A66">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>65</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>66</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
                 </anchor>

--- a/AAAGameData/Languages/Hindi.xlsx
+++ b/AAAGameData/Languages/Hindi.xlsx
@@ -11,124 +11,144 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <d:author xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">Anonymous</d:author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0">
-      <text>
-        <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <rPr>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t xml:space="preserve">勾选锁定此行,锁定后将强制保留</t>
-        </d:r>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0">
-      <text>
-        <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <rPr>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t xml:space="preserve">多语言Key</t>
-        </d:r>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0">
-      <text>
-        <d:r xmlns:d="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <rPr>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t xml:space="preserve">多语言Value, 当值为空时, [一键翻译]会自动填充Value值</t>
-        </d:r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
   <si>
     <t>AddBallsUIForm.ballTxt</t>
   </si>
   <si>
-    <t/>
+    <t>+5 गेंदें</t>
   </si>
   <si>
     <t>AddBallsUIForm.continueTxt</t>
   </si>
   <si>
+    <t>जारी रखें?</t>
+  </si>
+  <si>
     <t>ArrowMazeOverUIForm.GameOver</t>
   </si>
   <si>
+    <t>लगातार जीतने की चुनौती में असफल</t>
+  </si>
+  <si>
     <t>ArrowMazeOverUIForm.restart</t>
   </si>
   <si>
+    <t>फिर से शुरू करें</t>
+  </si>
+  <si>
     <t>ArrowMazeOverUIForm.Revive</t>
   </si>
   <si>
+    <t>पुनर्जीवित हों</t>
+  </si>
+  <si>
     <t>ArrowPrivacyPolicyUIForm.title</t>
   </si>
   <si>
+    <t>गोपनीयता नीति</t>
+  </si>
+  <si>
     <t>ArrowRewardDialogUIForm.claim</t>
   </si>
   <si>
+    <t>प्राप्त करें</t>
+  </si>
+  <si>
     <t>ArrowRewardDialogUIForm.Continue</t>
   </si>
   <si>
+    <t>जारी रखें</t>
+  </si>
+  <si>
     <t>ArrowRewardDialogUIForm.NextLevel</t>
   </si>
   <si>
+    <t>अगला स्तर</t>
+  </si>
+  <si>
     <t>ArrowRewardDialogUIForm.titletxt</t>
   </si>
   <si>
+    <t>कॉम्बो पुरस्कार</t>
+  </si>
+  <si>
     <t>ArrowRewardDialogUIForm.winTitle</t>
   </si>
   <si>
+    <t>स्तर पूरा हुआ</t>
+  </si>
+  <si>
     <t>ArrowRewardUIForm.titletxt</t>
   </si>
   <si>
+    <t>बधाई हो</t>
+  </si>
+  <si>
     <t>ArrowSettingController.OFF</t>
   </si>
   <si>
+    <t>बंद</t>
+  </si>
+  <si>
     <t>ArrowSettingController.ON</t>
   </si>
   <si>
+    <t>चालू</t>
+  </si>
+  <si>
     <t>ArrowSettingDialog.Home</t>
   </si>
   <si>
+    <t>होम</t>
+  </si>
+  <si>
     <t>ArrowSettingDialog.Music</t>
   </si>
   <si>
+    <t>संगीत</t>
+  </si>
+  <si>
     <t>ArrowSettingDialog.Privacy</t>
   </si>
   <si>
     <t>ArrowSettingDialog.Resume</t>
   </si>
   <si>
+    <t>फिर से जारी रखें</t>
+  </si>
+  <si>
     <t>ArrowSettingDialog.Sound</t>
   </si>
   <si>
+    <t>ध्वनि</t>
+  </si>
+  <si>
     <t>ArrowSettingDialog.Text_Title</t>
   </si>
   <si>
+    <t>सेटिंग्स</t>
+  </si>
+  <si>
     <t>ArrowSettingDialog.Vibrate</t>
   </si>
   <si>
+    <t>कंपन</t>
+  </si>
+  <si>
     <t>ArrowUITopbar.cashOut</t>
   </si>
   <si>
+    <t>रिडीम करें</t>
+  </si>
+  <si>
     <t>ArrowWithdrawalInfoItem.infoTxt</t>
   </si>
   <si>
+    <t>खिलाड़ी {0} को ({1}) पार करने और {2} प्राप्त करने पर बधाई।</t>
+  </si>
+  <si>
     <t>claim</t>
   </si>
   <si>
@@ -138,33 +158,63 @@
     <t>Enteraccountnumber</t>
   </si>
   <si>
+    <t>अपना खाता दर्ज करें</t>
+  </si>
+  <si>
     <t>EnterCPF</t>
   </si>
   <si>
+    <t>CPF दर्ज करें</t>
+  </si>
+  <si>
     <t>Enteremail</t>
   </si>
   <si>
+    <t>ईमेल की पुष्टि करें</t>
+  </si>
+  <si>
     <t>EnterFullName</t>
   </si>
   <si>
+    <t>पूरा नाम दर्ज करें</t>
+  </si>
+  <si>
     <t>EnterPayPalaccount</t>
   </si>
   <si>
+    <t>PayPal खाता दर्ज करें</t>
+  </si>
+  <si>
     <t>GuidTxt1</t>
   </si>
   <si>
+    <t>हिलाने के लिए टैप करें</t>
+  </si>
+  <si>
     <t>GuidTxt3</t>
   </si>
   <si>
+    <t xml:space="preserve">पैसे निकालने के लिए यहाँ टैप करें </t>
+  </si>
+  <si>
     <t>GuidTxt4</t>
   </si>
   <si>
+    <t>ज़ूम करने के लिए उँगलियाँ फैलाएँ</t>
+  </si>
+  <si>
     <t>GuidTxt5</t>
   </si>
   <si>
+    <t xml:space="preserve">अपना वर्तमान बैलेंस यहाँ देखें। </t>
+  </si>
+  <si>
     <t>GuidTxt6</t>
   </si>
   <si>
+    <t>पैसे निकालने के लिए शर्तें पूरी करें।</t>
+  </si>
+  <si>
     <t>HallTabUIForm.home</t>
   </si>
   <si>
@@ -174,78 +224,150 @@
     <t>HallTabUIForm.task</t>
   </si>
   <si>
+    <t>कार्य</t>
+  </si>
+  <si>
     <t>InfoErrTips1</t>
   </si>
   <si>
+    <t>कृपया एक मान्य ईमेल पता दर्ज करें</t>
+  </si>
+  <si>
     <t>InfoErrTips2</t>
   </si>
   <si>
+    <t>कृपया एक मान्य CPF दर्ज करें</t>
+  </si>
+  <si>
     <t>InfoErrTips3</t>
   </si>
   <si>
+    <t>PayPal खाते के लिए एक मान्य ईमेल पता आवश्यक है</t>
+  </si>
+  <si>
     <t>InfoErrTips4</t>
   </si>
   <si>
+    <t>कृपया अपना पूरा नाम दर्ज करें</t>
+  </si>
+  <si>
     <t>InfoErrTips5</t>
   </si>
   <si>
+    <t>कृपया अपना खाता नंबर दर्ज करें</t>
+  </si>
+  <si>
     <t>InfoErrTips6</t>
   </si>
   <si>
+    <t>कृपया भुगतान का तरीका चुनें</t>
+  </si>
+  <si>
     <t>InfoErrTips7</t>
   </si>
   <si>
+    <t>भुगतान की जानकारी सफलतापूर्वक सहेजी गई</t>
+  </si>
+  <si>
     <t>level</t>
   </si>
   <si>
+    <t>स्तर {0}</t>
+  </si>
+  <si>
     <t>LevelCompleteUIForm.complete</t>
   </si>
   <si>
     <t>LevelCompleteUIForm.next</t>
   </si>
   <si>
+    <t>अगला</t>
+  </si>
+  <si>
     <t>MakeUpFail</t>
   </si>
   <si>
+    <t>हमें खेद है, रिडीम नहीं हो सका।</t>
+  </si>
+  <si>
     <t>makeupInfoHint1</t>
   </si>
   <si>
+    <t>कृपया सुनिश्चित करें कि दोनों बार दर्ज किया गया PayPal खाता एक जैसा है।</t>
+  </si>
+  <si>
     <t>makeupInfoHint2</t>
   </si>
   <si>
+    <t>कृपया ईमेल सही प्रारूप में दर्ज करें।</t>
+  </si>
+  <si>
     <t>MakeupPaymentUIForm.desc</t>
   </si>
   <si>
+    <t>निकासी जारी है</t>
+  </si>
+  <si>
     <t>MakeupPaymentUIForm.titletxt</t>
   </si>
   <si>
+    <t>भुगतान का तरीका</t>
+  </si>
+  <si>
     <t>MakeUpStep1</t>
   </si>
   <si>
+    <t>पैसे निकालने के लिए स्तर {0} पार करें</t>
+  </si>
+  <si>
     <t>MakeUpStep2</t>
   </si>
   <si>
+    <t>पैसे निकालने के लिए {0} और इकट्ठा करें</t>
+  </si>
+  <si>
     <t>MakeupUIForm.input</t>
   </si>
   <si>
+    <t>दर्ज करें</t>
+  </si>
+  <si>
     <t>MakeupUIForm.record</t>
   </si>
   <si>
+    <t>इतिहास</t>
+  </si>
+  <si>
     <t>MakeupUIForm.title</t>
   </si>
   <si>
+    <t>पैसे निकालें</t>
+  </si>
+  <si>
     <t>MakeupUIForm.txtBalance</t>
   </si>
   <si>
+    <t>बैलेंस {0}=$1</t>
+  </si>
+  <si>
     <t>PcardGiftUIForm.desc</t>
   </si>
   <si>
+    <t>विज्ञापन देखें और संदूक से गेम की वस्तुएँ पाएँ।</t>
+  </si>
+  <si>
     <t>QuitConfirmUIForm.desc</t>
   </si>
   <si>
+    <t>अभी छोड़ने पर एक जीवन कम हो जाएगा।</t>
+  </si>
+  <si>
     <t>QuitConfirmUIForm.quitTxt</t>
   </si>
   <si>
+    <t>छोड़ें?</t>
+  </si>
+  <si>
     <t>SettingPageUIForm.continue</t>
   </si>
   <si>
@@ -255,7 +377,13 @@
     <t>SettingPageUIForm.quit</t>
   </si>
   <si>
+    <t>छोड़ें</t>
+  </si>
+  <si>
     <t>TaskItem.infoTxt</t>
+  </si>
+  <si>
+    <t>{0} स्तर जीतें!</t>
   </si>
 </sst>
 </file>
@@ -291,9 +419,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
+    <xf numFmtId="49" applyNumberFormat="1" fontId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -463,7 +589,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp46.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp47.xml><?xml version="1.0" encoding="utf-8"?>
@@ -569,2902 +695,6 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -3479,12 +709,12 @@
           <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1092">
+            <xdr:cNvPr hidden="1" name="A1" id="1025">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1092"/>
+                  <a14:compatExt spid="_x0000_s1025"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3565,12 +795,12 @@
           <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1093">
+            <xdr:cNvPr hidden="1" name="A2" id="1026">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1093"/>
+                  <a14:compatExt spid="_x0000_s1026"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3651,12 +881,12 @@
           <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1094">
+            <xdr:cNvPr hidden="1" name="A3" id="1027">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1094"/>
+                  <a14:compatExt spid="_x0000_s1027"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3737,12 +967,12 @@
           <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1095">
+            <xdr:cNvPr hidden="1" name="A4" id="1028">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1095"/>
+                  <a14:compatExt spid="_x0000_s1028"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3823,12 +1053,12 @@
           <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1096">
+            <xdr:cNvPr hidden="1" name="A5" id="1029">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1096"/>
+                  <a14:compatExt spid="_x0000_s1029"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3909,12 +1139,12 @@
           <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1097">
+            <xdr:cNvPr hidden="1" name="A6" id="1030">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1097"/>
+                  <a14:compatExt spid="_x0000_s1030"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -3995,12 +1225,12 @@
           <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1098">
+            <xdr:cNvPr hidden="1" name="A7" id="1031">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1098"/>
+                  <a14:compatExt spid="_x0000_s1031"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4081,12 +1311,12 @@
           <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1099">
+            <xdr:cNvPr hidden="1" name="A8" id="1032">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1099"/>
+                  <a14:compatExt spid="_x0000_s1032"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4167,12 +1397,12 @@
           <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1100">
+            <xdr:cNvPr hidden="1" name="A9" id="1033">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1100"/>
+                  <a14:compatExt spid="_x0000_s1033"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4253,12 +1483,12 @@
           <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1101">
+            <xdr:cNvPr hidden="1" name="A10" id="1034">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1101"/>
+                  <a14:compatExt spid="_x0000_s1034"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4339,12 +1569,12 @@
           <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1102">
+            <xdr:cNvPr hidden="1" name="A11" id="1035">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1102"/>
+                  <a14:compatExt spid="_x0000_s1035"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4425,12 +1655,12 @@
           <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1103">
+            <xdr:cNvPr hidden="1" name="A12" id="1036">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1103"/>
+                  <a14:compatExt spid="_x0000_s1036"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4511,12 +1741,12 @@
           <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1104">
+            <xdr:cNvPr hidden="1" name="A13" id="1037">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1104"/>
+                  <a14:compatExt spid="_x0000_s1037"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4597,12 +1827,12 @@
           <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1105">
+            <xdr:cNvPr hidden="1" name="A14" id="1038">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1105"/>
+                  <a14:compatExt spid="_x0000_s1038"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4683,12 +1913,12 @@
           <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1106">
+            <xdr:cNvPr hidden="1" name="A15" id="1039">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1106"/>
+                  <a14:compatExt spid="_x0000_s1039"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4769,12 +1999,12 @@
           <xdr:row>16</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1107">
+            <xdr:cNvPr hidden="1" name="A16" id="1040">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1107"/>
+                  <a14:compatExt spid="_x0000_s1040"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4855,12 +2085,12 @@
           <xdr:row>17</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1108">
+            <xdr:cNvPr hidden="1" name="A17" id="1041">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1108"/>
+                  <a14:compatExt spid="_x0000_s1041"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4941,12 +2171,12 @@
           <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1109">
+            <xdr:cNvPr hidden="1" name="A18" id="1042">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1109"/>
+                  <a14:compatExt spid="_x0000_s1042"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5027,12 +2257,12 @@
           <xdr:row>19</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1110">
+            <xdr:cNvPr hidden="1" name="A19" id="1043">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1110"/>
+                  <a14:compatExt spid="_x0000_s1043"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5113,12 +2343,12 @@
           <xdr:row>20</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1111">
+            <xdr:cNvPr hidden="1" name="A20" id="1044">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1111"/>
+                  <a14:compatExt spid="_x0000_s1044"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5199,12 +2429,12 @@
           <xdr:row>21</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1112">
+            <xdr:cNvPr hidden="1" name="A21" id="1045">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1112"/>
+                  <a14:compatExt spid="_x0000_s1045"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5285,12 +2515,12 @@
           <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1113">
+            <xdr:cNvPr hidden="1" name="A22" id="1046">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1113"/>
+                  <a14:compatExt spid="_x0000_s1046"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5371,12 +2601,12 @@
           <xdr:row>23</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1114">
+            <xdr:cNvPr hidden="1" name="A23" id="1047">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1114"/>
+                  <a14:compatExt spid="_x0000_s1047"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5457,12 +2687,12 @@
           <xdr:row>24</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A24" id="1115">
+            <xdr:cNvPr hidden="1" name="A24" id="1048">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1115"/>
+                  <a14:compatExt spid="_x0000_s1048"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5543,12 +2773,12 @@
           <xdr:row>25</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A25" id="1116">
+            <xdr:cNvPr hidden="1" name="A25" id="1049">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1116"/>
+                  <a14:compatExt spid="_x0000_s1049"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5629,12 +2859,12 @@
           <xdr:row>26</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A26" id="1117">
+            <xdr:cNvPr hidden="1" name="A26" id="1050">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1117"/>
+                  <a14:compatExt spid="_x0000_s1050"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5715,12 +2945,12 @@
           <xdr:row>27</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A27" id="1118">
+            <xdr:cNvPr hidden="1" name="A27" id="1051">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1118"/>
+                  <a14:compatExt spid="_x0000_s1051"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5801,12 +3031,12 @@
           <xdr:row>28</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A28" id="1119">
+            <xdr:cNvPr hidden="1" name="A28" id="1052">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1119"/>
+                  <a14:compatExt spid="_x0000_s1052"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5887,12 +3117,12 @@
           <xdr:row>29</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A29" id="1120">
+            <xdr:cNvPr hidden="1" name="A29" id="1053">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1120"/>
+                  <a14:compatExt spid="_x0000_s1053"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5973,12 +3203,12 @@
           <xdr:row>30</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A30" id="1121">
+            <xdr:cNvPr hidden="1" name="A30" id="1054">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1121"/>
+                  <a14:compatExt spid="_x0000_s1054"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6059,12 +3289,12 @@
           <xdr:row>31</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A31" id="1122">
+            <xdr:cNvPr hidden="1" name="A31" id="1055">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1122"/>
+                  <a14:compatExt spid="_x0000_s1055"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6145,12 +3375,12 @@
           <xdr:row>32</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A32" id="1123">
+            <xdr:cNvPr hidden="1" name="A32" id="1056">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1123"/>
+                  <a14:compatExt spid="_x0000_s1056"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6231,12 +3461,12 @@
           <xdr:row>33</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A33" id="1124">
+            <xdr:cNvPr hidden="1" name="A33" id="1057">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1124"/>
+                  <a14:compatExt spid="_x0000_s1057"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6317,12 +3547,12 @@
           <xdr:row>34</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A34" id="1125">
+            <xdr:cNvPr hidden="1" name="A34" id="1058">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1125"/>
+                  <a14:compatExt spid="_x0000_s1058"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6403,12 +3633,12 @@
           <xdr:row>35</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A35" id="1126">
+            <xdr:cNvPr hidden="1" name="A35" id="1059">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1126"/>
+                  <a14:compatExt spid="_x0000_s1059"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6489,12 +3719,12 @@
           <xdr:row>36</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A36" id="1127">
+            <xdr:cNvPr hidden="1" name="A36" id="1060">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1127"/>
+                  <a14:compatExt spid="_x0000_s1060"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6575,12 +3805,12 @@
           <xdr:row>37</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A37" id="1128">
+            <xdr:cNvPr hidden="1" name="A37" id="1061">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1128"/>
+                  <a14:compatExt spid="_x0000_s1061"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6661,12 +3891,12 @@
           <xdr:row>38</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A38" id="1129">
+            <xdr:cNvPr hidden="1" name="A38" id="1062">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1129"/>
+                  <a14:compatExt spid="_x0000_s1062"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6747,12 +3977,12 @@
           <xdr:row>39</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A39" id="1130">
+            <xdr:cNvPr hidden="1" name="A39" id="1063">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1130"/>
+                  <a14:compatExt spid="_x0000_s1063"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6833,12 +4063,12 @@
           <xdr:row>40</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A40" id="1131">
+            <xdr:cNvPr hidden="1" name="A40" id="1064">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1131"/>
+                  <a14:compatExt spid="_x0000_s1064"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -6919,12 +4149,12 @@
           <xdr:row>41</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A41" id="1132">
+            <xdr:cNvPr hidden="1" name="A41" id="1065">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1132"/>
+                  <a14:compatExt spid="_x0000_s1065"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7005,12 +4235,12 @@
           <xdr:row>42</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A42" id="1133">
+            <xdr:cNvPr hidden="1" name="A42" id="1066">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1133"/>
+                  <a14:compatExt spid="_x0000_s1066"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7091,12 +4321,12 @@
           <xdr:row>43</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A43" id="1134">
+            <xdr:cNvPr hidden="1" name="A43" id="1067">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1134"/>
+                  <a14:compatExt spid="_x0000_s1067"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7177,12 +4407,12 @@
           <xdr:row>44</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A44" id="1135">
+            <xdr:cNvPr hidden="1" name="A44" id="1068">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1135"/>
+                  <a14:compatExt spid="_x0000_s1068"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7263,12 +4493,12 @@
           <xdr:row>45</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A45" id="1136">
+            <xdr:cNvPr hidden="1" name="A45" id="1069">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1136"/>
+                  <a14:compatExt spid="_x0000_s1069"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7349,12 +4579,12 @@
           <xdr:row>46</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A46" id="1137">
+            <xdr:cNvPr hidden="1" name="A46" id="1070">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1137"/>
+                  <a14:compatExt spid="_x0000_s1070"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7435,12 +4665,12 @@
           <xdr:row>47</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A47" id="1138">
+            <xdr:cNvPr hidden="1" name="A47" id="1071">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1138"/>
+                  <a14:compatExt spid="_x0000_s1071"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7521,12 +4751,12 @@
           <xdr:row>48</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A48" id="1139">
+            <xdr:cNvPr hidden="1" name="A48" id="1072">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1139"/>
+                  <a14:compatExt spid="_x0000_s1072"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7607,12 +4837,12 @@
           <xdr:row>49</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A49" id="1140">
+            <xdr:cNvPr hidden="1" name="A49" id="1073">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1140"/>
+                  <a14:compatExt spid="_x0000_s1073"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7693,12 +4923,12 @@
           <xdr:row>50</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A50" id="1141">
+            <xdr:cNvPr hidden="1" name="A50" id="1074">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1141"/>
+                  <a14:compatExt spid="_x0000_s1074"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7779,12 +5009,12 @@
           <xdr:row>51</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A51" id="1142">
+            <xdr:cNvPr hidden="1" name="A51" id="1075">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1142"/>
+                  <a14:compatExt spid="_x0000_s1075"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7865,12 +5095,12 @@
           <xdr:row>52</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A52" id="1143">
+            <xdr:cNvPr hidden="1" name="A52" id="1076">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1143"/>
+                  <a14:compatExt spid="_x0000_s1076"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -7951,12 +5181,12 @@
           <xdr:row>53</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A53" id="1144">
+            <xdr:cNvPr hidden="1" name="A53" id="1077">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1144"/>
+                  <a14:compatExt spid="_x0000_s1077"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8037,12 +5267,12 @@
           <xdr:row>54</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A54" id="1145">
+            <xdr:cNvPr hidden="1" name="A54" id="1078">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1145"/>
+                  <a14:compatExt spid="_x0000_s1078"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8123,12 +5353,12 @@
           <xdr:row>55</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A55" id="1146">
+            <xdr:cNvPr hidden="1" name="A55" id="1079">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1146"/>
+                  <a14:compatExt spid="_x0000_s1079"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8209,12 +5439,12 @@
           <xdr:row>56</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A56" id="1147">
+            <xdr:cNvPr hidden="1" name="A56" id="1080">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1147"/>
+                  <a14:compatExt spid="_x0000_s1080"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8295,12 +5525,12 @@
           <xdr:row>57</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A57" id="1148">
+            <xdr:cNvPr hidden="1" name="A57" id="1081">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1148"/>
+                  <a14:compatExt spid="_x0000_s1081"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8381,12 +5611,12 @@
           <xdr:row>58</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A58" id="1149">
+            <xdr:cNvPr hidden="1" name="A58" id="1082">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1149"/>
+                  <a14:compatExt spid="_x0000_s1082"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8467,12 +5697,12 @@
           <xdr:row>59</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A59" id="1150">
+            <xdr:cNvPr hidden="1" name="A59" id="1083">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1150"/>
+                  <a14:compatExt spid="_x0000_s1083"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8553,12 +5783,12 @@
           <xdr:row>60</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A60" id="1151">
+            <xdr:cNvPr hidden="1" name="A60" id="1084">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1151"/>
+                  <a14:compatExt spid="_x0000_s1084"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8639,12 +5869,12 @@
           <xdr:row>61</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A61" id="1152">
+            <xdr:cNvPr hidden="1" name="A61" id="1085">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1152"/>
+                  <a14:compatExt spid="_x0000_s1085"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8725,12 +5955,12 @@
           <xdr:row>62</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A62" id="1153">
+            <xdr:cNvPr hidden="1" name="A62" id="1086">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1153"/>
+                  <a14:compatExt spid="_x0000_s1086"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8811,12 +6041,12 @@
           <xdr:row>63</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A63" id="1154">
+            <xdr:cNvPr hidden="1" name="A63" id="1087">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1154"/>
+                  <a14:compatExt spid="_x0000_s1087"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8897,12 +6127,12 @@
           <xdr:row>64</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A64" id="1155">
+            <xdr:cNvPr hidden="1" name="A64" id="1088">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1155"/>
+                  <a14:compatExt spid="_x0000_s1088"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -8983,12 +6213,12 @@
           <xdr:row>65</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A65" id="1156">
+            <xdr:cNvPr hidden="1" name="A65" id="1089">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1156"/>
+                  <a14:compatExt spid="_x0000_s1089"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9069,12 +6299,12 @@
           <xdr:row>66</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
+        <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A66" id="1157">
+            <xdr:cNvPr hidden="1" name="A66" id="1090">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1157"/>
+                  <a14:compatExt spid="_x0000_s1090"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -9148,603 +6378,538 @@
   <dimension ref="A1:C66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="34.0738721575056" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="1" max="1" width="8" customWidth="1" style="1"/>
+    <col min="2" max="2" width="45" customWidth="1" style="1"/>
+    <col min="3" max="3" width="60" customWidth="1" style="1"/>
+    <col min="4" max="16384" width="9.140625" customWidth="1" style="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1"/>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1"/>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>1</v>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>1</v>
+      <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1"/>
-      <c r="B4" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>1</v>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1"/>
-      <c r="B5" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>1</v>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1"/>
-      <c r="B6" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>1</v>
+      <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1"/>
-      <c r="B7" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>1</v>
+      <c r="B7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1"/>
-      <c r="B8" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>1</v>
+      <c r="B8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1"/>
-      <c r="B9" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>1</v>
+      <c r="B9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1"/>
-      <c r="B10" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>1</v>
+      <c r="B10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1"/>
-      <c r="B11" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="0" t="s">
-        <v>1</v>
+      <c r="B11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1"/>
-      <c r="B12" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="0" t="s">
-        <v>1</v>
+      <c r="B12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1"/>
-      <c r="B13" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="0" t="s">
-        <v>1</v>
+      <c r="B13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1"/>
-      <c r="B14" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="0" t="s">
-        <v>1</v>
+      <c r="B14" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1"/>
-      <c r="B15" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="0" t="s">
-        <v>1</v>
+      <c r="B15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1"/>
-      <c r="B16" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="0" t="s">
-        <v>1</v>
+      <c r="B16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1"/>
-      <c r="B17" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="0" t="s">
-        <v>1</v>
+      <c r="B17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1"/>
-      <c r="B18" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="0" t="s">
-        <v>1</v>
+      <c r="B18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1"/>
-      <c r="B19" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="C19" s="0" t="s">
-        <v>1</v>
+      <c r="B19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1"/>
-      <c r="B20" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="0" t="s">
-        <v>1</v>
+      <c r="B20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1"/>
-      <c r="B21" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="0" t="s">
-        <v>1</v>
+      <c r="B21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1"/>
-      <c r="B22" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="0" t="s">
-        <v>1</v>
+      <c r="B22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1"/>
-      <c r="B23" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" s="0" t="s">
-        <v>1</v>
+      <c r="B23" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1"/>
-      <c r="B24" s="0" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="0" t="s">
-        <v>1</v>
+      <c r="B24" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="C25" s="0" t="s">
-        <v>1</v>
+      <c r="B25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1"/>
-      <c r="B26" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="0" t="s">
-        <v>1</v>
+      <c r="B26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1"/>
-      <c r="B27" s="0" t="s">
-        <v>27</v>
-      </c>
-      <c r="C27" s="0" t="s">
-        <v>1</v>
+      <c r="B27" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1"/>
-      <c r="B28" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="C28" s="0" t="s">
-        <v>1</v>
+      <c r="B28" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1"/>
-      <c r="B29" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="C29" s="0" t="s">
-        <v>1</v>
+      <c r="B29" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1"/>
-      <c r="B30" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="C30" s="0" t="s">
-        <v>1</v>
+      <c r="B30" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1"/>
-      <c r="B31" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="0" t="s">
-        <v>1</v>
+      <c r="B31" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1"/>
-      <c r="B32" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32" s="0" t="s">
-        <v>1</v>
+      <c r="B32" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1"/>
-      <c r="B33" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" s="0" t="s">
-        <v>1</v>
+      <c r="B33" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1"/>
-      <c r="B34" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="C34" s="0" t="s">
-        <v>1</v>
+      <c r="B34" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1"/>
-      <c r="B35" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="C35" s="0" t="s">
-        <v>1</v>
+      <c r="B35" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1"/>
-      <c r="B36" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="C36" s="0" t="s">
-        <v>1</v>
+      <c r="B36" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1"/>
-      <c r="B37" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="C37" s="0" t="s">
-        <v>1</v>
+      <c r="B37" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1"/>
-      <c r="B38" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="C38" s="0" t="s">
-        <v>1</v>
+      <c r="B38" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1"/>
-      <c r="B39" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="C39" s="0" t="s">
-        <v>1</v>
+      <c r="B39" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1"/>
-      <c r="B40" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="C40" s="0" t="s">
-        <v>1</v>
+      <c r="B40" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1"/>
-      <c r="B41" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="C41" s="0" t="s">
-        <v>1</v>
+      <c r="B41" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1"/>
-      <c r="B42" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="C42" s="0" t="s">
-        <v>1</v>
+      <c r="B42" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1"/>
-      <c r="B43" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="C43" s="0" t="s">
-        <v>1</v>
+      <c r="B43" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1"/>
-      <c r="B44" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="C44" s="0" t="s">
-        <v>1</v>
+      <c r="B44" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1"/>
-      <c r="B45" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="C45" s="0" t="s">
-        <v>1</v>
+      <c r="B45" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1"/>
-      <c r="B46" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="C46" s="0" t="s">
-        <v>1</v>
+      <c r="B46" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1"/>
-      <c r="B47" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C47" s="0" t="s">
-        <v>1</v>
+      <c r="B47" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1"/>
-      <c r="B48" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C48" s="0" t="s">
-        <v>1</v>
+      <c r="B48" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1"/>
-      <c r="B49" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C49" s="0" t="s">
-        <v>1</v>
+      <c r="B49" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1"/>
-      <c r="B50" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C50" s="0" t="s">
-        <v>1</v>
+      <c r="B50" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1"/>
-      <c r="B51" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="C51" s="0" t="s">
-        <v>1</v>
+      <c r="B51" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1"/>
-      <c r="B52" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="C52" s="0" t="s">
-        <v>1</v>
+      <c r="B52" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1"/>
-      <c r="B53" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="C53" s="0" t="s">
-        <v>1</v>
+      <c r="B53" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1"/>
-      <c r="B54" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C54" s="0" t="s">
-        <v>1</v>
+      <c r="B54" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1"/>
-      <c r="B55" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C55" s="0" t="s">
-        <v>1</v>
+      <c r="B55" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1"/>
-      <c r="B56" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C56" s="0" t="s">
-        <v>1</v>
+      <c r="B56" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1"/>
-      <c r="B57" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="C57" s="0" t="s">
-        <v>1</v>
+      <c r="B57" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1"/>
-      <c r="B58" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="C58" s="0" t="s">
-        <v>1</v>
+      <c r="B58" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1"/>
-      <c r="B59" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="C59" s="0" t="s">
-        <v>1</v>
+      <c r="B59" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1"/>
-      <c r="B60" s="0" t="s">
-        <v>60</v>
-      </c>
-      <c r="C60" s="0" t="s">
-        <v>1</v>
+      <c r="B60" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1"/>
-      <c r="B61" s="0" t="s">
-        <v>61</v>
-      </c>
-      <c r="C61" s="0" t="s">
-        <v>1</v>
+      <c r="B61" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1"/>
-      <c r="B62" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="C62" s="0" t="s">
-        <v>1</v>
+      <c r="B62" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1"/>
-      <c r="B63" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="C63" s="0" t="s">
-        <v>1</v>
+      <c r="B63" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1"/>
-      <c r="B64" s="0" t="s">
-        <v>64</v>
-      </c>
-      <c r="C64" s="0" t="s">
-        <v>1</v>
+      <c r="B64" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1"/>
-      <c r="B65" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="C65" s="0" t="s">
-        <v>1</v>
+      <c r="B65" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1"/>
-      <c r="B66" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="C66" s="0" t="s">
-        <v>1</v>
+      <c r="B66" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -9756,7 +6921,7 @@
       <controls xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1092" r:id="rId717" name="A1">
+            <control shapeId="1025" r:id="rId2" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9778,7 +6943,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId718" name="A2">
+            <control shapeId="1026" r:id="rId4" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9800,7 +6965,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId719" name="A3">
+            <control shapeId="1027" r:id="rId5" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9822,7 +6987,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId720" name="A4">
+            <control shapeId="1028" r:id="rId6" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9844,7 +7009,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId721" name="A5">
+            <control shapeId="1029" r:id="rId7" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9866,7 +7031,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId722" name="A6">
+            <control shapeId="1030" r:id="rId8" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9888,7 +7053,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId723" name="A7">
+            <control shapeId="1031" r:id="rId9" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9910,7 +7075,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId724" name="A8">
+            <control shapeId="1032" r:id="rId10" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9932,7 +7097,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId725" name="A9">
+            <control shapeId="1033" r:id="rId11" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9954,7 +7119,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId726" name="A10">
+            <control shapeId="1034" r:id="rId12" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9976,7 +7141,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId727" name="A11">
+            <control shapeId="1035" r:id="rId13" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -9998,7 +7163,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId728" name="A12">
+            <control shapeId="1036" r:id="rId14" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10020,7 +7185,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId729" name="A13">
+            <control shapeId="1037" r:id="rId15" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10042,7 +7207,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId730" name="A14">
+            <control shapeId="1038" r:id="rId16" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10064,7 +7229,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId731" name="A15">
+            <control shapeId="1039" r:id="rId17" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10086,7 +7251,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId732" name="A16">
+            <control shapeId="1040" r:id="rId18" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10108,7 +7273,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId733" name="A17">
+            <control shapeId="1041" r:id="rId19" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10130,7 +7295,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId734" name="A18">
+            <control shapeId="1042" r:id="rId20" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10152,7 +7317,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId735" name="A19">
+            <control shapeId="1043" r:id="rId21" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10174,7 +7339,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1111" r:id="rId736" name="A20">
+            <control shapeId="1044" r:id="rId22" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10196,7 +7361,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1112" r:id="rId737" name="A21">
+            <control shapeId="1045" r:id="rId23" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10218,7 +7383,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1113" r:id="rId738" name="A22">
+            <control shapeId="1046" r:id="rId24" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10240,7 +7405,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1114" r:id="rId739" name="A23">
+            <control shapeId="1047" r:id="rId25" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10262,7 +7427,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1115" r:id="rId740" name="A24">
+            <control shapeId="1048" r:id="rId26" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10284,7 +7449,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1116" r:id="rId741" name="A25">
+            <control shapeId="1049" r:id="rId27" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10306,7 +7471,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1117" r:id="rId742" name="A26">
+            <control shapeId="1050" r:id="rId28" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10328,7 +7493,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1118" r:id="rId743" name="A27">
+            <control shapeId="1051" r:id="rId29" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10350,7 +7515,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1119" r:id="rId744" name="A28">
+            <control shapeId="1052" r:id="rId30" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10372,7 +7537,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1120" r:id="rId745" name="A29">
+            <control shapeId="1053" r:id="rId31" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10394,7 +7559,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1121" r:id="rId746" name="A30">
+            <control shapeId="1054" r:id="rId32" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10416,7 +7581,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1122" r:id="rId747" name="A31">
+            <control shapeId="1055" r:id="rId33" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10438,7 +7603,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1123" r:id="rId748" name="A32">
+            <control shapeId="1056" r:id="rId34" name="A32">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10460,7 +7625,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1124" r:id="rId749" name="A33">
+            <control shapeId="1057" r:id="rId35" name="A33">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10482,7 +7647,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1125" r:id="rId750" name="A34">
+            <control shapeId="1058" r:id="rId36" name="A34">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10504,7 +7669,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1126" r:id="rId751" name="A35">
+            <control shapeId="1059" r:id="rId37" name="A35">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10526,7 +7691,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1127" r:id="rId752" name="A36">
+            <control shapeId="1060" r:id="rId38" name="A36">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10548,7 +7713,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1128" r:id="rId753" name="A37">
+            <control shapeId="1061" r:id="rId39" name="A37">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10570,7 +7735,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1129" r:id="rId754" name="A38">
+            <control shapeId="1062" r:id="rId40" name="A38">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10592,7 +7757,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1130" r:id="rId755" name="A39">
+            <control shapeId="1063" r:id="rId41" name="A39">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10614,7 +7779,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1131" r:id="rId756" name="A40">
+            <control shapeId="1064" r:id="rId42" name="A40">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10636,7 +7801,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1132" r:id="rId757" name="A41">
+            <control shapeId="1065" r:id="rId43" name="A41">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10658,7 +7823,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1133" r:id="rId758" name="A42">
+            <control shapeId="1066" r:id="rId44" name="A42">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10680,7 +7845,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1134" r:id="rId759" name="A43">
+            <control shapeId="1067" r:id="rId45" name="A43">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10702,7 +7867,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1135" r:id="rId760" name="A44">
+            <control shapeId="1068" r:id="rId46" name="A44">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10724,7 +7889,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1136" r:id="rId761" name="A45">
+            <control shapeId="1069" r:id="rId47" name="A45">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10746,7 +7911,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1137" r:id="rId762" name="A46">
+            <control shapeId="1070" r:id="rId48" name="A46">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10768,7 +7933,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1138" r:id="rId763" name="A47">
+            <control shapeId="1071" r:id="rId49" name="A47">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10790,7 +7955,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1139" r:id="rId764" name="A48">
+            <control shapeId="1072" r:id="rId50" name="A48">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10812,7 +7977,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1140" r:id="rId765" name="A49">
+            <control shapeId="1073" r:id="rId51" name="A49">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10834,7 +7999,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1141" r:id="rId766" name="A50">
+            <control shapeId="1074" r:id="rId52" name="A50">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10856,7 +8021,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1142" r:id="rId767" name="A51">
+            <control shapeId="1075" r:id="rId53" name="A51">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10878,7 +8043,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1143" r:id="rId768" name="A52">
+            <control shapeId="1076" r:id="rId54" name="A52">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10900,7 +8065,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1144" r:id="rId769" name="A53">
+            <control shapeId="1077" r:id="rId55" name="A53">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10922,7 +8087,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1145" r:id="rId770" name="A54">
+            <control shapeId="1078" r:id="rId56" name="A54">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10944,7 +8109,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1146" r:id="rId771" name="A55">
+            <control shapeId="1079" r:id="rId57" name="A55">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10966,7 +8131,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1147" r:id="rId772" name="A56">
+            <control shapeId="1080" r:id="rId58" name="A56">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -10988,7 +8153,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1148" r:id="rId773" name="A57">
+            <control shapeId="1081" r:id="rId59" name="A57">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11010,7 +8175,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1149" r:id="rId774" name="A58">
+            <control shapeId="1082" r:id="rId60" name="A58">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11032,7 +8197,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1150" r:id="rId775" name="A59">
+            <control shapeId="1083" r:id="rId61" name="A59">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11054,7 +8219,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1151" r:id="rId776" name="A60">
+            <control shapeId="1084" r:id="rId62" name="A60">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11076,7 +8241,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1152" r:id="rId777" name="A61">
+            <control shapeId="1085" r:id="rId63" name="A61">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11098,7 +8263,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1153" r:id="rId778" name="A62">
+            <control shapeId="1086" r:id="rId64" name="A62">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11120,7 +8285,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1154" r:id="rId779" name="A63">
+            <control shapeId="1087" r:id="rId65" name="A63">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11142,7 +8307,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1155" r:id="rId780" name="A64">
+            <control shapeId="1088" r:id="rId66" name="A64">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11164,7 +8329,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1156" r:id="rId781" name="A65">
+            <control shapeId="1089" r:id="rId67" name="A65">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -11186,7 +8351,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1157" r:id="rId782" name="A66">
+            <control shapeId="1090" r:id="rId68" name="A66">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>

--- a/AAAGameData/Languages/Hindi.xlsx
+++ b/AAAGameData/Languages/Hindi.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
   <si>
     <t>AddBallsUIForm.ballTxt</t>
   </si>
@@ -140,7 +140,7 @@
     <t>ArrowUITopbar.cashOut</t>
   </si>
   <si>
-    <t>रिडीम करें</t>
+    <t>निकासी करें</t>
   </si>
   <si>
     <t>ArrowWithdrawalInfoItem.infoTxt</t>
@@ -384,6 +384,9 @@
   </si>
   <si>
     <t>{0} स्तर जीतें!</t>
+  </si>
+  <si>
+    <t>MakeupRecordUIForm.title</t>
   </si>
 </sst>
 </file>
@@ -680,6 +683,10 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp67.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -6370,12 +6377,98 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>66</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>67</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A67" id="1091">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1091"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C66"/>
+  <dimension ref="A1:C67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1" style="1"/>
@@ -6910,6 +7003,14 @@
       </c>
       <c r="C66" s="1" t="s">
         <v>123</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -8371,6 +8472,28 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1091" r:id="rId69" name="A67">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>66</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>67</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/Hindi.xlsx
+++ b/AAAGameData/Languages/Hindi.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
   <si>
     <t>AddBallsUIForm.ballTxt</t>
   </si>
@@ -278,6 +278,9 @@
     <t>LevelCompleteUIForm.complete</t>
   </si>
   <si>
+    <t>पूरा हुआ</t>
+  </si>
+  <si>
     <t>LevelCompleteUIForm.next</t>
   </si>
   <si>
@@ -387,6 +390,69 @@
   </si>
   <si>
     <t>MakeupRecordUIForm.title</t>
+  </si>
+  <si>
+    <t>AddLifeUIForm.titleTxt</t>
+  </si>
+  <si>
+    <t>अतिरिक्त जीवन</t>
+  </si>
+  <si>
+    <t>AddPropUIForm.titleTxt</t>
+  </si>
+  <si>
+    <t>रॉकेट</t>
+  </si>
+  <si>
+    <t>PlayLoadingUIForm.loading</t>
+  </si>
+  <si>
+    <t>लोड हो रहा है...</t>
+  </si>
+  <si>
+    <t>QuitConfirmUIForm.quit</t>
+  </si>
+  <si>
+    <t>MakeupInfoUIForm.avatarTxt</t>
+  </si>
+  <si>
+    <t>अवतार चुनें:</t>
+  </si>
+  <si>
+    <t>MakeupInfoUIForm.enterDesc</t>
+  </si>
+  <si>
+    <t>अपना PayPal खाता दर्ज करें</t>
+  </si>
+  <si>
+    <t>MakeupInfoUIForm.enterAgainDesc</t>
+  </si>
+  <si>
+    <t>PayPal खाता फिर से दर्ज करें</t>
+  </si>
+  <si>
+    <t>MakeupInfoUIForm.confirm</t>
+  </si>
+  <si>
+    <t>पुष्टि करें</t>
+  </si>
+  <si>
+    <t>TaskItem.adTxt</t>
+  </si>
+  <si>
+    <t>विज्ञापन देखें!</t>
+  </si>
+  <si>
+    <t>free</t>
+  </si>
+  <si>
+    <t>मुफ़्त</t>
+  </si>
+  <si>
+    <t>TaskItem.go</t>
+  </si>
+  <si>
+    <t>जाएँ</t>
   </si>
 </sst>
 </file>
@@ -687,7 +753,51 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp68.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp69.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp70.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp71.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp72.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp73.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp74.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp75.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp76.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp77.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp78.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -6463,12 +6573,958 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>67</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>68</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A68" id="1092">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1092"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>68</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>69</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A69" id="1093">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1093"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>69</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>70</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A70" id="1094">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1094"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>70</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>71</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A71" id="1095">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1095"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>71</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>72</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A72" id="1096">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1096"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>72</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>73</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A73" id="1097">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1097"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>73</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>74</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A74" id="1098">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1098"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>74</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>75</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A75" id="1099">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1099"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>75</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>76</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A76" id="1100">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1100"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>76</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>77</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A77" id="1101">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1101"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>77</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>78</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A78" id="1102">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1102"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C67"/>
+  <dimension ref="A1:C78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1" style="1"/>
@@ -6850,132 +7906,132 @@
         <v>87</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>15</v>
@@ -6983,7 +8039,7 @@
     </row>
     <row r="64">
       <c r="B64" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>11</v>
@@ -6991,26 +8047,114 @@
     </row>
     <row r="65">
       <c r="B65" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -8494,6 +9638,248 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1092" r:id="rId70" name="A68">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>67</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>68</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1093" r:id="rId71" name="A69">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>68</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>69</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1094" r:id="rId72" name="A70">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>69</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>70</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1095" r:id="rId73" name="A71">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>70</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>71</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1096" r:id="rId74" name="A72">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>71</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>72</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1097" r:id="rId75" name="A73">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>72</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>73</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1098" r:id="rId76" name="A74">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>73</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>74</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1099" r:id="rId77" name="A75">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>74</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>75</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1100" r:id="rId78" name="A76">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>75</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>76</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1101" r:id="rId79" name="A77">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>76</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>77</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1102" r:id="rId80" name="A78">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>77</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>78</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/Hindi.xlsx
+++ b/AAAGameData/Languages/Hindi.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="150">
   <si>
     <t>AddBallsUIForm.ballTxt</t>
   </si>
@@ -453,6 +453,15 @@
   </si>
   <si>
     <t>जाएँ</t>
+  </si>
+  <si>
+    <t>cashoutHint</t>
+  </si>
+  <si>
+    <t>इसे प्राप्त करने के लिए आपको {0} स्तर पार करने होंगे और अपना बैलेंस {1} तक पहुँचाना होगा।</t>
+  </si>
+  <si>
+    <t>MakeupItem.cashout</t>
   </si>
 </sst>
 </file>
@@ -801,7 +810,15 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp79.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp80.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -7519,12 +7536,184 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>78</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>79</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A79" id="1103">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1103"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>79</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>80</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A80" id="1104">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1104"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C78"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1" style="1"/>
@@ -8155,6 +8344,22 @@
       </c>
       <c r="C78" s="1" t="s">
         <v>146</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -9880,6 +10085,50 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1103" r:id="rId81" name="A79">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>78</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>79</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1104" r:id="rId82" name="A80">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>79</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>80</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/Hindi.xlsx
+++ b/AAAGameData/Languages/Hindi.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
   <si>
     <t>AddBallsUIForm.ballTxt</t>
   </si>
@@ -188,7 +188,7 @@
     <t>GuidTxt1</t>
   </si>
   <si>
-    <t>हिलाने के लिए टैप करें</t>
+    <t>उस वस्तु पर टैप करें और तोप चलाएँ!</t>
   </si>
   <si>
     <t>GuidTxt3</t>
@@ -462,6 +462,42 @@
   </si>
   <si>
     <t>MakeupItem.cashout</t>
+  </si>
+  <si>
+    <t>GuidTxt2</t>
+  </si>
+  <si>
+    <t>गोले खत्म होने से पहले सभी वस्तुएँ हटाएँ!</t>
+  </si>
+  <si>
+    <t>MakeupRecordItem.bouns</t>
+  </si>
+  <si>
+    <t>आज की कुल पुरस्कार राशि</t>
+  </si>
+  <si>
+    <t>PlayUIForm.txtHint</t>
+  </si>
+  <si>
+    <t>मेज़ पर रखी वस्तुओं पर टैप करें</t>
+  </si>
+  <si>
+    <t>MakeupItem.reach</t>
+  </si>
+  <si>
+    <t>आवश्यक बैलेंस</t>
+  </si>
+  <si>
+    <t>PrelevelUIForm.desc</t>
+  </si>
+  <si>
+    <t>बूस्टर चुनें:</t>
+  </si>
+  <si>
+    <t>MakeupPaymentEndUIForm.desc</t>
+  </si>
+  <si>
+    <t>आपके उदार दान के लिए धन्यवाद!</t>
   </si>
 </sst>
 </file>
@@ -607,19 +643,19 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp32.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp33.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp35.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp36.xml><?xml version="1.0" encoding="utf-8"?>
@@ -822,6 +858,30 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp81.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp82.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp83.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp84.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp85.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp86.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp9.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -7708,12 +7768,528 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>80</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>81</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A81" id="1105">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1105"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>81</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>82</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A82" id="1106">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1106"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>82</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>83</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A83" id="1107">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1107"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>83</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>84</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A84" id="1108">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1108"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>84</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>85</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A85" id="1109">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1109"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>85</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>86</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A86" id="1110">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1110"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C80"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1" style="1"/>
@@ -8360,6 +8936,54 @@
       </c>
       <c r="C80" s="1" t="s">
         <v>42</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -10129,6 +10753,138 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1105" r:id="rId83" name="A81">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>80</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>81</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1106" r:id="rId84" name="A82">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>81</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>82</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1107" r:id="rId85" name="A83">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>82</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>83</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1108" r:id="rId86" name="A84">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>83</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>84</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1109" r:id="rId87" name="A85">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>84</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>85</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1110" r:id="rId88" name="A86">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>85</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>86</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/Hindi.xlsx
+++ b/AAAGameData/Languages/Hindi.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
   <si>
     <t>AddBallsUIForm.ballTxt</t>
   </si>
@@ -26,24 +26,6 @@
     <t>जारी रखें?</t>
   </si>
   <si>
-    <t>ArrowMazeOverUIForm.GameOver</t>
-  </si>
-  <si>
-    <t>लगातार जीतने की चुनौती में असफल</t>
-  </si>
-  <si>
-    <t>ArrowMazeOverUIForm.restart</t>
-  </si>
-  <si>
-    <t>फिर से शुरू करें</t>
-  </si>
-  <si>
-    <t>ArrowMazeOverUIForm.Revive</t>
-  </si>
-  <si>
-    <t>पुनर्जीवित हों</t>
-  </si>
-  <si>
     <t>ArrowPrivacyPolicyUIForm.title</t>
   </si>
   <si>
@@ -56,322 +38,244 @@
     <t>प्राप्त करें</t>
   </si>
   <si>
-    <t>ArrowRewardDialogUIForm.Continue</t>
+    <t>ArrowRewardUIForm.titletxt</t>
+  </si>
+  <si>
+    <t>बधाई हो</t>
+  </si>
+  <si>
+    <t>ArrowSettingController.OFF</t>
+  </si>
+  <si>
+    <t>बंद</t>
+  </si>
+  <si>
+    <t>ArrowSettingController.ON</t>
+  </si>
+  <si>
+    <t>चालू</t>
+  </si>
+  <si>
+    <t>ArrowUITopbar.cashOut</t>
+  </si>
+  <si>
+    <t>निकासी करें</t>
+  </si>
+  <si>
+    <t>ArrowWithdrawalInfoItem.infoTxt</t>
+  </si>
+  <si>
+    <t>खिलाड़ी {0} को ({1}) पार करने और {2} प्राप्त करने पर बधाई।</t>
+  </si>
+  <si>
+    <t>claim</t>
+  </si>
+  <si>
+    <t>CoinRewardUIForm.titletxt</t>
+  </si>
+  <si>
+    <t>Enteraccountnumber</t>
+  </si>
+  <si>
+    <t>अपना खाता दर्ज करें</t>
+  </si>
+  <si>
+    <t>EnterCPF</t>
+  </si>
+  <si>
+    <t>CPF दर्ज करें</t>
+  </si>
+  <si>
+    <t>Enteremail</t>
+  </si>
+  <si>
+    <t>ईमेल की पुष्टि करें</t>
+  </si>
+  <si>
+    <t>EnterFullName</t>
+  </si>
+  <si>
+    <t>पूरा नाम दर्ज करें</t>
+  </si>
+  <si>
+    <t>EnterPayPalaccount</t>
+  </si>
+  <si>
+    <t>PayPal खाता दर्ज करें</t>
+  </si>
+  <si>
+    <t>GuidTxt1</t>
+  </si>
+  <si>
+    <t>उस वस्तु पर टैप करें और तोप चलाएँ!</t>
+  </si>
+  <si>
+    <t>HallTabUIForm.home</t>
+  </si>
+  <si>
+    <t>होम</t>
+  </si>
+  <si>
+    <t>HallTabUIForm.setting</t>
+  </si>
+  <si>
+    <t>सेटिंग्स</t>
+  </si>
+  <si>
+    <t>HallTabUIForm.task</t>
+  </si>
+  <si>
+    <t>कार्य</t>
+  </si>
+  <si>
+    <t>InfoErrTips1</t>
+  </si>
+  <si>
+    <t>कृपया एक मान्य ईमेल पता दर्ज करें</t>
+  </si>
+  <si>
+    <t>InfoErrTips2</t>
+  </si>
+  <si>
+    <t>कृपया एक मान्य CPF दर्ज करें</t>
+  </si>
+  <si>
+    <t>InfoErrTips3</t>
+  </si>
+  <si>
+    <t>PayPal खाते के लिए एक मान्य ईमेल पता आवश्यक है</t>
+  </si>
+  <si>
+    <t>InfoErrTips4</t>
+  </si>
+  <si>
+    <t>कृपया अपना पूरा नाम दर्ज करें</t>
+  </si>
+  <si>
+    <t>InfoErrTips5</t>
+  </si>
+  <si>
+    <t>कृपया अपना खाता नंबर दर्ज करें</t>
+  </si>
+  <si>
+    <t>InfoErrTips6</t>
+  </si>
+  <si>
+    <t>कृपया भुगतान का तरीका चुनें</t>
+  </si>
+  <si>
+    <t>InfoErrTips7</t>
+  </si>
+  <si>
+    <t>भुगतान की जानकारी सफलतापूर्वक सहेजी गई</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>स्तर {0}</t>
+  </si>
+  <si>
+    <t>LevelCompleteUIForm.complete</t>
+  </si>
+  <si>
+    <t>पूरा हुआ</t>
+  </si>
+  <si>
+    <t>LevelCompleteUIForm.next</t>
+  </si>
+  <si>
+    <t>अगला</t>
+  </si>
+  <si>
+    <t>MakeUpFail</t>
+  </si>
+  <si>
+    <t>हमें खेद है, रिडीम नहीं हो सका।</t>
+  </si>
+  <si>
+    <t>makeupInfoHint1</t>
+  </si>
+  <si>
+    <t>कृपया सुनिश्चित करें कि दोनों बार दर्ज किया गया PayPal खाता एक जैसा है।</t>
+  </si>
+  <si>
+    <t>makeupInfoHint2</t>
+  </si>
+  <si>
+    <t>कृपया ईमेल सही प्रारूप में दर्ज करें।</t>
+  </si>
+  <si>
+    <t>MakeupPaymentUIForm.desc</t>
+  </si>
+  <si>
+    <t>निकासी जारी है</t>
+  </si>
+  <si>
+    <t>MakeupPaymentUIForm.titletxt</t>
+  </si>
+  <si>
+    <t>भुगतान का तरीका</t>
+  </si>
+  <si>
+    <t>MakeUpStep1</t>
+  </si>
+  <si>
+    <t>पैसे निकालने के लिए स्तर {0} पार करें</t>
+  </si>
+  <si>
+    <t>MakeUpStep2</t>
+  </si>
+  <si>
+    <t>पैसे निकालने के लिए {0} और इकट्ठा करें</t>
+  </si>
+  <si>
+    <t>MakeupUIForm.input</t>
+  </si>
+  <si>
+    <t>दर्ज करें</t>
+  </si>
+  <si>
+    <t>MakeupUIForm.record</t>
+  </si>
+  <si>
+    <t>इतिहास</t>
+  </si>
+  <si>
+    <t>MakeupUIForm.title</t>
+  </si>
+  <si>
+    <t>पैसे निकालें</t>
+  </si>
+  <si>
+    <t>MakeupUIForm.txtBalance</t>
+  </si>
+  <si>
+    <t>बैलेंस {0}=$1</t>
+  </si>
+  <si>
+    <t>PcardGiftUIForm.desc</t>
+  </si>
+  <si>
+    <t>विज्ञापन देखें और संदूक से गेम की वस्तुएँ पाएँ।</t>
+  </si>
+  <si>
+    <t>QuitConfirmUIForm.desc</t>
+  </si>
+  <si>
+    <t>अभी छोड़ने पर एक जीवन कम हो जाएगा।</t>
+  </si>
+  <si>
+    <t>QuitConfirmUIForm.quitTxt</t>
+  </si>
+  <si>
+    <t>छोड़ें?</t>
+  </si>
+  <si>
+    <t>SettingPageUIForm.continue</t>
   </si>
   <si>
     <t>जारी रखें</t>
-  </si>
-  <si>
-    <t>ArrowRewardDialogUIForm.NextLevel</t>
-  </si>
-  <si>
-    <t>अगला स्तर</t>
-  </si>
-  <si>
-    <t>ArrowRewardDialogUIForm.titletxt</t>
-  </si>
-  <si>
-    <t>कॉम्बो पुरस्कार</t>
-  </si>
-  <si>
-    <t>ArrowRewardDialogUIForm.winTitle</t>
-  </si>
-  <si>
-    <t>स्तर पूरा हुआ</t>
-  </si>
-  <si>
-    <t>ArrowRewardUIForm.titletxt</t>
-  </si>
-  <si>
-    <t>बधाई हो</t>
-  </si>
-  <si>
-    <t>ArrowSettingController.OFF</t>
-  </si>
-  <si>
-    <t>बंद</t>
-  </si>
-  <si>
-    <t>ArrowSettingController.ON</t>
-  </si>
-  <si>
-    <t>चालू</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Home</t>
-  </si>
-  <si>
-    <t>होम</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Music</t>
-  </si>
-  <si>
-    <t>संगीत</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Privacy</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Resume</t>
-  </si>
-  <si>
-    <t>फिर से जारी रखें</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Sound</t>
-  </si>
-  <si>
-    <t>ध्वनि</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Text_Title</t>
-  </si>
-  <si>
-    <t>सेटिंग्स</t>
-  </si>
-  <si>
-    <t>ArrowSettingDialog.Vibrate</t>
-  </si>
-  <si>
-    <t>कंपन</t>
-  </si>
-  <si>
-    <t>ArrowUITopbar.cashOut</t>
-  </si>
-  <si>
-    <t>निकासी करें</t>
-  </si>
-  <si>
-    <t>ArrowWithdrawalInfoItem.infoTxt</t>
-  </si>
-  <si>
-    <t>खिलाड़ी {0} को ({1}) पार करने और {2} प्राप्त करने पर बधाई।</t>
-  </si>
-  <si>
-    <t>claim</t>
-  </si>
-  <si>
-    <t>CoinRewardUIForm.titletxt</t>
-  </si>
-  <si>
-    <t>Enteraccountnumber</t>
-  </si>
-  <si>
-    <t>अपना खाता दर्ज करें</t>
-  </si>
-  <si>
-    <t>EnterCPF</t>
-  </si>
-  <si>
-    <t>CPF दर्ज करें</t>
-  </si>
-  <si>
-    <t>Enteremail</t>
-  </si>
-  <si>
-    <t>ईमेल की पुष्टि करें</t>
-  </si>
-  <si>
-    <t>EnterFullName</t>
-  </si>
-  <si>
-    <t>पूरा नाम दर्ज करें</t>
-  </si>
-  <si>
-    <t>EnterPayPalaccount</t>
-  </si>
-  <si>
-    <t>PayPal खाता दर्ज करें</t>
-  </si>
-  <si>
-    <t>GuidTxt1</t>
-  </si>
-  <si>
-    <t>उस वस्तु पर टैप करें और तोप चलाएँ!</t>
-  </si>
-  <si>
-    <t>GuidTxt3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">पैसे निकालने के लिए यहाँ टैप करें </t>
-  </si>
-  <si>
-    <t>GuidTxt4</t>
-  </si>
-  <si>
-    <t>ज़ूम करने के लिए उँगलियाँ फैलाएँ</t>
-  </si>
-  <si>
-    <t>GuidTxt5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">अपना वर्तमान बैलेंस यहाँ देखें। </t>
-  </si>
-  <si>
-    <t>GuidTxt6</t>
-  </si>
-  <si>
-    <t>पैसे निकालने के लिए शर्तें पूरी करें।</t>
-  </si>
-  <si>
-    <t>HallTabUIForm.home</t>
-  </si>
-  <si>
-    <t>HallTabUIForm.setting</t>
-  </si>
-  <si>
-    <t>HallTabUIForm.task</t>
-  </si>
-  <si>
-    <t>कार्य</t>
-  </si>
-  <si>
-    <t>InfoErrTips1</t>
-  </si>
-  <si>
-    <t>कृपया एक मान्य ईमेल पता दर्ज करें</t>
-  </si>
-  <si>
-    <t>InfoErrTips2</t>
-  </si>
-  <si>
-    <t>कृपया एक मान्य CPF दर्ज करें</t>
-  </si>
-  <si>
-    <t>InfoErrTips3</t>
-  </si>
-  <si>
-    <t>PayPal खाते के लिए एक मान्य ईमेल पता आवश्यक है</t>
-  </si>
-  <si>
-    <t>InfoErrTips4</t>
-  </si>
-  <si>
-    <t>कृपया अपना पूरा नाम दर्ज करें</t>
-  </si>
-  <si>
-    <t>InfoErrTips5</t>
-  </si>
-  <si>
-    <t>कृपया अपना खाता नंबर दर्ज करें</t>
-  </si>
-  <si>
-    <t>InfoErrTips6</t>
-  </si>
-  <si>
-    <t>कृपया भुगतान का तरीका चुनें</t>
-  </si>
-  <si>
-    <t>InfoErrTips7</t>
-  </si>
-  <si>
-    <t>भुगतान की जानकारी सफलतापूर्वक सहेजी गई</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>स्तर {0}</t>
-  </si>
-  <si>
-    <t>LevelCompleteUIForm.complete</t>
-  </si>
-  <si>
-    <t>पूरा हुआ</t>
-  </si>
-  <si>
-    <t>LevelCompleteUIForm.next</t>
-  </si>
-  <si>
-    <t>अगला</t>
-  </si>
-  <si>
-    <t>MakeUpFail</t>
-  </si>
-  <si>
-    <t>हमें खेद है, रिडीम नहीं हो सका।</t>
-  </si>
-  <si>
-    <t>makeupInfoHint1</t>
-  </si>
-  <si>
-    <t>कृपया सुनिश्चित करें कि दोनों बार दर्ज किया गया PayPal खाता एक जैसा है।</t>
-  </si>
-  <si>
-    <t>makeupInfoHint2</t>
-  </si>
-  <si>
-    <t>कृपया ईमेल सही प्रारूप में दर्ज करें।</t>
-  </si>
-  <si>
-    <t>MakeupPaymentUIForm.desc</t>
-  </si>
-  <si>
-    <t>निकासी जारी है</t>
-  </si>
-  <si>
-    <t>MakeupPaymentUIForm.titletxt</t>
-  </si>
-  <si>
-    <t>भुगतान का तरीका</t>
-  </si>
-  <si>
-    <t>MakeUpStep1</t>
-  </si>
-  <si>
-    <t>पैसे निकालने के लिए स्तर {0} पार करें</t>
-  </si>
-  <si>
-    <t>MakeUpStep2</t>
-  </si>
-  <si>
-    <t>पैसे निकालने के लिए {0} और इकट्ठा करें</t>
-  </si>
-  <si>
-    <t>MakeupUIForm.input</t>
-  </si>
-  <si>
-    <t>दर्ज करें</t>
-  </si>
-  <si>
-    <t>MakeupUIForm.record</t>
-  </si>
-  <si>
-    <t>इतिहास</t>
-  </si>
-  <si>
-    <t>MakeupUIForm.title</t>
-  </si>
-  <si>
-    <t>पैसे निकालें</t>
-  </si>
-  <si>
-    <t>MakeupUIForm.txtBalance</t>
-  </si>
-  <si>
-    <t>बैलेंस {0}=$1</t>
-  </si>
-  <si>
-    <t>PcardGiftUIForm.desc</t>
-  </si>
-  <si>
-    <t>विज्ञापन देखें और संदूक से गेम की वस्तुएँ पाएँ।</t>
-  </si>
-  <si>
-    <t>QuitConfirmUIForm.desc</t>
-  </si>
-  <si>
-    <t>अभी छोड़ने पर एक जीवन कम हो जाएगा।</t>
-  </si>
-  <si>
-    <t>QuitConfirmUIForm.quitTxt</t>
-  </si>
-  <si>
-    <t>छोड़ें?</t>
-  </si>
-  <si>
-    <t>SettingPageUIForm.continue</t>
   </si>
   <si>
     <t>SettingPageUIForm.privacy</t>
@@ -555,27 +459,27 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
@@ -595,23 +499,23 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp26.xml><?xml version="1.0" encoding="utf-8"?>
@@ -627,7 +531,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp29.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -635,7 +539,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp30.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp31.xml><?xml version="1.0" encoding="utf-8"?>
@@ -643,11 +547,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp32.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp33.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp34.xml><?xml version="1.0" encoding="utf-8"?>
@@ -659,11 +563,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp36.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp37.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp38.xml><?xml version="1.0" encoding="utf-8"?>
@@ -671,7 +575,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp39.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -679,31 +583,31 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp40.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp41.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp42.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp43.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp44.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp45.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp46.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp47.xml><?xml version="1.0" encoding="utf-8"?>
@@ -715,7 +619,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp49.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp5.xml><?xml version="1.0" encoding="utf-8"?>
@@ -723,11 +627,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp50.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp51.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp52.xml><?xml version="1.0" encoding="utf-8"?>
@@ -739,11 +643,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp54.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp55.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp56.xml><?xml version="1.0" encoding="utf-8"?>
@@ -771,7 +675,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp61.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp62.xml><?xml version="1.0" encoding="utf-8"?>
@@ -779,7 +683,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp63.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp64.xml><?xml version="1.0" encoding="utf-8"?>
@@ -802,83 +706,11 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp69.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
-<file path=xl/ctrlProps/ctrlProp70.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp71.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp72.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp73.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp74.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp75.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp76.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp77.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp78.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp79.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp80.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp81.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp82.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp83.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp84.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp85.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
-</file>
-
-<file path=xl/ctrlProps/ctrlProp86.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -6736,1560 +6568,12 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>68</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>69</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A69" id="1093">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1093"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>69</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>70</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A70" id="1094">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1094"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>70</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>71</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A71" id="1095">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1095"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>71</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>72</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A72" id="1096">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1096"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>72</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>73</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A73" id="1097">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1097"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>73</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>74</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A74" id="1098">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1098"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>74</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>75</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A75" id="1099">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1099"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>75</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>76</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A76" id="1100">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1100"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>76</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>77</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A77" id="1101">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1101"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>77</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>78</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A78" id="1102">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1102"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>78</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>79</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A79" id="1103">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1103"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>79</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>80</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A80" id="1104">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1104"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>80</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>81</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A81" id="1105">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1105"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>81</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>82</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A82" id="1106">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1106"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>82</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>83</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A83" id="1107">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1107"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>83</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>84</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A84" id="1108">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1108"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>84</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>85</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A85" id="1109">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1109"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>85</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>86</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A86" id="1110">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1110"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C86"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1" style="1"/>
@@ -8375,119 +6659,119 @@
         <v>18</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="25">
@@ -8495,231 +6779,231 @@
         <v>46</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="1" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>86</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54">
@@ -8791,15 +7075,15 @@
         <v>117</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>118</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="64">
@@ -8807,183 +7091,39 @@
         <v>120</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>11</v>
+        <v>121</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="C69" s="1" t="s">
         <v>129</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="B75" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="B81" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="B85" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -10489,402 +8629,6 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1093" r:id="rId71" name="A69">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>68</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>69</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1094" r:id="rId72" name="A70">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>69</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>70</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1095" r:id="rId73" name="A71">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>70</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>71</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1096" r:id="rId74" name="A72">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>71</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>72</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1097" r:id="rId75" name="A73">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>72</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>73</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1098" r:id="rId76" name="A74">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>73</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>74</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1099" r:id="rId77" name="A75">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>74</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>75</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1100" r:id="rId78" name="A76">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>75</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>76</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1101" r:id="rId79" name="A77">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>76</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>77</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1102" r:id="rId80" name="A78">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>77</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>78</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1103" r:id="rId81" name="A79">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>78</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>79</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1104" r:id="rId82" name="A80">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>79</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>80</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1105" r:id="rId83" name="A81">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>80</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>81</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1106" r:id="rId84" name="A82">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>81</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>82</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1107" r:id="rId85" name="A83">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>82</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>83</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1108" r:id="rId86" name="A84">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>83</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>84</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1109" r:id="rId87" name="A85">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>84</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>85</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
-        <mc:AlternateContent>
-          <mc:Choice Requires="x14">
-            <control shapeId="1110" r:id="rId88" name="A86">
-              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
-                <anchor moveWithCells="1">
-                  <from>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>85</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </from>
-                  <to>
-                    <xdr:col>0</xdr:col>
-                    <xdr:colOff>285750</xdr:colOff>
-                    <xdr:row>86</xdr:row>
-                    <xdr:rowOff>0</xdr:rowOff>
-                  </to>
-                </anchor>
-              </controlPr>
-            </control>
-          </mc:Choice>
-        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>

--- a/AAAGameData/Languages/Hindi.xlsx
+++ b/AAAGameData/Languages/Hindi.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="132">
   <si>
     <t>AddBallsUIForm.ballTxt</t>
   </si>
@@ -402,6 +402,12 @@
   </si>
   <si>
     <t>आपके उदार दान के लिए धन्यवाद!</t>
+  </si>
+  <si>
+    <t>giftHint</t>
+  </si>
+  <si>
+    <t>खज़ाने के संदूक इकट्ठा करें</t>
   </si>
 </sst>
 </file>
@@ -706,6 +712,10 @@
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp69.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
@@ -6568,12 +6578,98 @@
     </mc:Choice>
     <mc:Fallback/>
   </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>68</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>69</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A69" id="1093">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1093"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
 </xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:C68"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1" style="1"/>
@@ -7124,6 +7220,14 @@
       </c>
       <c r="C68" s="1" t="s">
         <v>129</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -8629,6 +8733,28 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1093" r:id="rId71" name="A69">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>68</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>69</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </Choice>
   </AlternateContent>
